--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,6 +219,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,173 +586,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:BI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="2.6" customWidth="1" min="7" max="7"/>
-    <col width="2.6" customWidth="1" min="8" max="8"/>
-    <col width="2.6" customWidth="1" min="9" max="9"/>
-    <col width="2.6" customWidth="1" min="10" max="10"/>
-    <col width="2.6" customWidth="1" min="11" max="11"/>
-    <col width="2.6" customWidth="1" min="12" max="12"/>
-    <col width="2.6" customWidth="1" min="13" max="13"/>
-    <col width="2.6" customWidth="1" min="14" max="14"/>
-    <col width="2.6" customWidth="1" min="15" max="15"/>
-    <col width="2.6" customWidth="1" min="16" max="16"/>
-    <col width="2.6" customWidth="1" min="17" max="17"/>
-    <col width="2.6" customWidth="1" min="18" max="18"/>
-    <col width="2.6" customWidth="1" min="19" max="19"/>
-    <col width="2.6" customWidth="1" min="20" max="20"/>
-    <col width="2.6" customWidth="1" min="21" max="21"/>
-    <col width="2.6" customWidth="1" min="22" max="22"/>
-    <col width="2.6" customWidth="1" min="23" max="23"/>
-    <col width="2.6" customWidth="1" min="24" max="24"/>
-    <col width="2.6" customWidth="1" min="25" max="25"/>
-    <col width="2.6" customWidth="1" min="26" max="26"/>
-    <col width="2.6" customWidth="1" min="27" max="27"/>
-    <col width="2.6" customWidth="1" min="28" max="28"/>
-    <col width="2.6" customWidth="1" min="29" max="29"/>
-    <col width="2.6" customWidth="1" min="30" max="30"/>
-    <col width="2.6" customWidth="1" min="31" max="31"/>
-    <col width="2.6" customWidth="1" min="32" max="32"/>
-    <col width="2.6" customWidth="1" min="33" max="33"/>
-    <col width="2.6" customWidth="1" min="34" max="34"/>
-    <col width="2.6" customWidth="1" min="35" max="35"/>
-    <col width="2.6" customWidth="1" min="36" max="36"/>
-    <col width="2.6" customWidth="1" min="37" max="37"/>
-    <col width="2.6" customWidth="1" min="38" max="38"/>
-    <col width="2.6" customWidth="1" min="39" max="39"/>
-    <col width="2.6" customWidth="1" min="40" max="40"/>
-    <col width="2.6" customWidth="1" min="41" max="41"/>
-    <col width="2.6" customWidth="1" min="42" max="42"/>
-    <col width="2.6" customWidth="1" min="43" max="43"/>
-    <col width="2.6" customWidth="1" min="44" max="44"/>
-    <col width="2.6" customWidth="1" min="45" max="45"/>
-    <col width="2.6" customWidth="1" min="46" max="46"/>
-    <col width="2.6" customWidth="1" min="47" max="47"/>
-    <col width="2.6" customWidth="1" min="48" max="48"/>
-    <col width="2.6" customWidth="1" min="49" max="49"/>
-    <col width="2.6" customWidth="1" min="50" max="50"/>
-    <col width="2.6" customWidth="1" min="51" max="51"/>
-    <col width="2.6" customWidth="1" min="52" max="52"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="2.6" customWidth="1" min="7" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t xml:space="preserve">Project</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>타노시미 투어 (tanoshimi) — 한일교류 여행 파티매칭 + 협업 플래너 + AI 추천 서비스</t>
+          <t xml:space="preserve">타노시미 투어 (tanoshimi) — 한일교류 여행 파티매칭 + 협업 플래너 + AI 추천 서비스</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>허수연(팀장), 김태민, 정태웅, 이동인, 오채원, 김민규</t>
+          <t xml:space="preserve">Write</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">허수연(팀장), 김태민, 정태웅, 이동인  (오채원·김민규 2026-09-15 이탈)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Issued date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
+          <t xml:space="preserve">Issued date</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t xml:space="preserve">Note</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>8/17~9/8은 실제 git 커밋 이력 기준 실적, 9/9 이후는 01_프로젝트_기획서 일정(P1 후반~P4)에 따른 계획입니다.</t>
+          <t xml:space="preserve">Jira TNSM 프로젝트(2026-10-05 조회) 기준. 시작일/종료일 = Jira 시작일·기한, 상태 = Jira 상태. * 표시는 시작일·기한이 없어 생성일·해결일로 대체한 행. 하위 작업은 업무 칸에 건수로 표시. 이탈 인원(오채원·김민규)의 잔여 티켓은 9/24 허수연에게 재배정되어 담당자가 허수연으로 표시됨.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Work Break-down Structure</t>
+          <t xml:space="preserve">Work Break-down Structure</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>구분(단계)</t>
+          <t xml:space="preserve">구분(단계)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>업무 / 산출물</t>
+          <t xml:space="preserve">업무 / 산출물</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t xml:space="preserve">담당자</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>시작일</t>
+          <t xml:space="preserve">시작일</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>종료일</t>
+          <t xml:space="preserve">종료일</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t xml:space="preserve">상태</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>8월</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8월</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>9월</t>
-        </is>
-      </c>
-      <c r="AC7" s="7" t="n"/>
+          <t xml:space="preserve">9월</t>
+        </is>
+      </c>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="6"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="6"/>
+      <c r="AN7" s="6"/>
+      <c r="AO7" s="6"/>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="6"/>
+      <c r="AR7" s="6"/>
+      <c r="AS7" s="6"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="6"/>
+      <c r="AV7" s="6"/>
+      <c r="AW7" s="6"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="6"/>
       <c r="AZ7" s="6" t="inlineStr">
         <is>
-          <t>10월</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10월</t>
+        </is>
+      </c>
+      <c r="BA7" s="6"/>
+      <c r="BB7" s="6"/>
+      <c r="BC7" s="6"/>
+      <c r="BD7" s="6"/>
+      <c r="BE7" s="6"/>
+      <c r="BF7" s="6"/>
+      <c r="BG7" s="6"/>
+      <c r="BH7" s="6"/>
+      <c r="BI7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="9" t="n">
         <v>17</v>
       </c>
@@ -817,7 +825,7 @@
       <c r="AB8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AC8" s="11" t="n">
+      <c r="AC8" s="9" t="n">
         <v>8</v>
       </c>
       <c r="AD8" s="9" t="n">
@@ -889,1434 +897,1242 @@
       <c r="AZ8" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="BA8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH8" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI8" s="10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>초기 프로젝트 셋업 · 프로토타입 스캐폴딩(제안서 v12 기준)</t>
+          <t xml:space="preserve">[TNSM-6] 팀 킥오프 · 역할 확정 · 하위 3건 중 완료 3</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>허수연</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="AC9" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="BD9" s="7"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>gitignore/빌드 캐시·비밀값 파일 정리</t>
+          <t xml:space="preserve">[TNSM-7] 기존 프로토타입 코드 리뷰(온보딩)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>정태웅</t>
+          <t xml:space="preserve">미배정</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t xml:space="preserve">2026-08-26</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="AC10" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="BD10" s="7"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>로그인 실패 잠금 수정 + 인증 도메인 v16 반영, 단위테스트 추가</t>
+          <t xml:space="preserve">[TNSM-8] ERD · API 설계 보완 · 하위 2건 중 완료 2, 취소 1</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="Q11" s="14" t="n"/>
-      <c r="AC11" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="BD11" s="7"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>인증 회귀 복구(실패카운트 리셋, LINE 재비활성화 등)</t>
+          <t xml:space="preserve">[TNSM-9] 개발환경 · 깃허브 레포 세팅 · 하위 4건 중 완료 4</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="U12" s="14" t="n"/>
-      <c r="AC12" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="BD12" s="7"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>비밀번호 재발급(임시비밀번호+강제변경) 구현</t>
+          <t xml:space="preserve">[TNSM-10] 와이어프레임 확정 · 하위 2건 모두 취소</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">미배정</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-08-26</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-08-30</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W13" s="14" t="n"/>
-      <c r="AC13" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="BD13" s="7"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>회원가입 본인인증 채널 SMS→이메일 전환</t>
+          <t xml:space="preserve">[TNSM-11] ① 로그인/소셜/휴대폰인증 검증·보강 · 하위 4건 중 완료 4</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">김태민</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W14" s="14" t="n"/>
-      <c r="AC14" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="14"/>
+      <c r="AF14" s="14"/>
+      <c r="AG14" s="14"/>
+      <c r="AH14" s="14"/>
+      <c r="BD14" s="7"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>소셜 로그인 이메일 인증 생략 처리 + 검증 보강</t>
+          <t xml:space="preserve">[TNSM-12] ② 실시간 동시편집 플래너 신규 개발 · 하위 5건 중 완료 5, 취소 1</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">정태웅</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W15" s="14" t="n"/>
-      <c r="AC15" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="14"/>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="14"/>
+      <c r="AH15" s="14"/>
+      <c r="BD15" s="7"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>LINE 소셜 로그인 재도입(Day5) + OIDC 서명검증 버그 수정</t>
+          <t xml:space="preserve">[TNSM-13] ③ 추천 로직 검증 + 임베딩 고도화 착수 · 하위 6건 중 완료 6</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">이동인</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X16" s="14" t="n"/>
-      <c r="AC16" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
+      <c r="AE16" s="14"/>
+      <c r="AF16" s="14"/>
+      <c r="AG16" s="14"/>
+      <c r="AH16" s="14"/>
+      <c r="AI16" s="14"/>
+      <c r="BD16" s="7"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>SocialLoginResolver 리팩터링 + 계정연동(social-link) 통합, 테스트 복구</t>
+          <t xml:space="preserve">[TNSM-14] ④ 게시판/리뷰/매칭/채팅 검증·보강 · 하위 6건 중 완료 6</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">오채원</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X17" s="14" t="n"/>
-      <c r="AC17" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="14"/>
+      <c r="AH17" s="14"/>
+      <c r="BD17" s="7"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>OAuth/SMTP 팀 공용 계정 필요사항 문서화(TODO)</t>
+          <t xml:space="preserve">[TNSM-15] [취소] ⑤ 1·2단계 분할결제/재고동시성/포인트 검증·보강 · 하위 4건 모두 취소</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X18" s="14" t="n"/>
-      <c r="AC18" s="7" t="n"/>
+          <t xml:space="preserve">취소</t>
+        </is>
+      </c>
+      <c r="BD18" s="7"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>P1-인증</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>이메일 중복 소셜로그인 안내문구 추가 + 예외처리 스코프 확장</t>
+          <t xml:space="preserve">[TNSM-16] [취소] ⑥ 마이페이지 검증 · 하위 2건 중 완료 2, 취소 1</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>김태민</t>
+          <t xml:space="preserve">김민규</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="AC19" s="15" t="n"/>
+          <t xml:space="preserve">취소</t>
+        </is>
+      </c>
+      <c r="BD19" s="7"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>P1-파티</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>v16 반영 + 결제 패키지 제거, 플래너 편집권한 설계</t>
+          <t xml:space="preserve">[TNSM-29] 매너온도 평가 로직 구현 *</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>정태웅</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="P20" s="14" t="n"/>
-      <c r="AC20" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="BD20" s="7"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>P1-파티</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>파티 게시판 필터 UI(성별/국적/연령/지역, TNSM-54)</t>
+          <t xml:space="preserve">[TNSM-82] ⑤ AI 동선 최적화 (고정/이동 일정 구분 기반 자동 경로 생성) · 하위 4건 중 완료 4 *</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>오채원</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X21" s="14" t="n"/>
-      <c r="AC21" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="BD21" s="7"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>P1-파티</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>파티 모집상태/D-day 뱃지 모순 수정 + 신청 가드 추가</t>
+          <t xml:space="preserve">[TNSM-17] 날씨 기반 재추천 흐름 · 하위 1건 중 완료 1, 취소 1</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>허수연</t>
+          <t xml:space="preserve">이동인</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W22" s="14" t="n"/>
-      <c r="X22" s="14" t="n"/>
-      <c r="AC22" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AI22" s="14"/>
+      <c r="AJ22" s="14"/>
+      <c r="AK22" s="14"/>
+      <c r="BD22" s="7"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>P1-파티</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>컨트롤러→서비스 리팩터링 Phase1~7(party/post/planner/chat/social/admin/profile)</t>
+          <t xml:space="preserve">[TNSM-18] 활동 이력 기반 추천</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>허수연</t>
+          <t xml:space="preserve">이동인</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X23" s="14" t="n"/>
-      <c r="AC23" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AI23" s="14"/>
+      <c r="AJ23" s="14"/>
+      <c r="AK23" s="14"/>
+      <c r="BD23" s="7"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>P1-플래너</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>AI 컴패니언 캐릭터(Live2D) 연동 + 렌더링 다수 버그 수정</t>
+          <t xml:space="preserve">[TNSM-19] 매너온도 노출 반영(읽기전용)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>정태웅</t>
+          <t xml:space="preserve">오채원</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="V24" s="14" t="n"/>
-      <c r="W24" s="14" t="n"/>
-      <c r="X24" s="14" t="n"/>
-      <c r="AC24" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AK24" s="14"/>
+      <c r="AL24" s="14"/>
+      <c r="AM24" s="14"/>
+      <c r="BD24" s="7"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>P1-플래너</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Gemini 실 클라이언트 추가, 여행 추천/리포트, 제출 시 AI 현실성 검토</t>
+          <t xml:space="preserve">[TNSM-20] 지도 정복 히트맵 + 칭호 시스템 · 하위 3건 중 완료 3, 취소 1</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>정태웅</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="V25" s="14" t="n"/>
-      <c r="AC25" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AI25" s="14"/>
+      <c r="AJ25" s="14"/>
+      <c r="AK25" s="14"/>
+      <c r="AL25" s="14"/>
+      <c r="AM25" s="14"/>
+      <c r="BD25" s="7"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>P1-플래너</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>동적 여행일수(일자 추가/삭제) 지원 + 리포지토리 참조 정리</t>
+          <t xml:space="preserve">[TNSM-21] 역할 간 연동 안정화 · 하위 1건 중 완료 1, 취소 1</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>정태웅</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-20</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X26" s="14" t="n"/>
-      <c r="AC26" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="14"/>
+      <c r="AM26" s="14"/>
+      <c r="AN26" s="14"/>
+      <c r="AO26" s="14"/>
+      <c r="BD26" s="7"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>P1-AI</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>PlannerController 트랜잭션 버그 수정</t>
+          <t xml:space="preserve">[TNSM-22] 1차 통합 QA</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>이동인</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-20</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="U27" s="14" t="n"/>
-      <c r="AC27" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AN27" s="14"/>
+      <c r="AO27" s="14"/>
+      <c r="BD27" s="7"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>P1-AI</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Gemini 기반 venue_type AI 판정 로직 + MockClient 분리</t>
+          <t xml:space="preserve">[TNSM-100] AI 현실성 검토 리포트 - feature/planner 머지 및 AI 실패 폴백 처리 *</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>이동인</t>
+          <t xml:space="preserve">정태웅</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="U28" s="14" t="n"/>
-      <c r="AC28" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AG28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="14"/>
+      <c r="AM28" s="14"/>
+      <c r="AN28" s="14"/>
+      <c r="AO28" s="14"/>
+      <c r="AP28" s="14"/>
+      <c r="AQ28" s="14"/>
+      <c r="AR28" s="14"/>
+      <c r="AS28" s="14"/>
+      <c r="BD28" s="7"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>P1-AI</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>날씨 기반 재추천, venue_type 버그 수정, ACTIVITY_NOT_FOUND 처리</t>
+          <t xml:space="preserve">[TNSM-101] 전체 화면 UI/CSS 스타일가이드 통일 *</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>이동인</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="U29" s="14" t="n"/>
-      <c r="AC29" s="7" t="n"/>
+          <t xml:space="preserve">할 일</t>
+        </is>
+      </c>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="16"/>
+      <c r="AK29" s="16"/>
+      <c r="AL29" s="16"/>
+      <c r="AM29" s="16"/>
+      <c r="AN29" s="16"/>
+      <c r="AO29" s="16"/>
+      <c r="AP29" s="16"/>
+      <c r="AQ29" s="16"/>
+      <c r="AR29" s="16"/>
+      <c r="AS29" s="16"/>
+      <c r="AT29" s="16"/>
+      <c r="AU29" s="16"/>
+      <c r="AV29" s="16"/>
+      <c r="AW29" s="16"/>
+      <c r="AX29" s="16"/>
+      <c r="AY29" s="16"/>
+      <c r="AZ29" s="16"/>
+      <c r="BA29" s="16"/>
+      <c r="BB29" s="16"/>
+      <c r="BC29" s="16"/>
+      <c r="BD29" s="19"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>P1-커뮤니티</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>유저 차단 기능 구현(TNSM-96)</t>
+          <t xml:space="preserve">[TNSM-23] 전체 시나리오 통합 테스트 &amp; 버그 수정 · 하위 2건 중 완료 1</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>오채원</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="V30" s="14" t="n"/>
-      <c r="AC30" s="7" t="n"/>
+          <t xml:space="preserve">할 일(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AP30" s="16"/>
+      <c r="AQ30" s="16"/>
+      <c r="AR30" s="16"/>
+      <c r="AS30" s="16"/>
+      <c r="BD30" s="7"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>P1-커뮤니티</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>게시판 댓글 대댓글(답글) UI(TNSM-52)</t>
+          <t xml:space="preserve">[TNSM-24] [취소] P2 기능 (선택) · 하위 3건 모두 취소</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>오채원</t>
+          <t xml:space="preserve">이동인</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X31" s="14" t="n"/>
-      <c r="AC31" s="7" t="n"/>
+          <t xml:space="preserve">취소</t>
+        </is>
+      </c>
+      <c r="BD31" s="7"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>히트맵 집계 전환, 자기소개 저장 API, 칭호 조건 개편</t>
+          <t xml:space="preserve">[TNSM-25] 발표자료 · 데모 시나리오 준비 · 하위 2건 중 완료 0</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="U32" s="14" t="n"/>
-      <c r="AC32" s="7" t="n"/>
+          <t xml:space="preserve">할 일(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AT32" s="16"/>
+      <c r="AU32" s="16"/>
+      <c r="AV32" s="16"/>
+      <c r="BD32" s="7"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>칭호 38종 개편, 지역별 스냅, 프로필 목업 반영</t>
+          <t xml:space="preserve">[TNSM-97] /mypage 500 — TitleService.allTitlesOrdered() NPE (category NULL 칭호) *</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">김민규</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="V33" s="14" t="n"/>
-      <c r="AC33" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="BD33" s="7"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>계정 관리 페이지(회원정보/소셜연동/알림/공개범위/차단) + vanity URL</t>
+          <t xml:space="preserve">[TNSM-98] GlobalExceptionHandler 스코프 누락 — @Controller+@ResponseBody 메서드의 예외가 스택트레이스로 노출 *</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W34" s="14" t="n"/>
-      <c r="AC34" s="7" t="n"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="14"/>
+      <c r="BD34" s="7"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>지도 스냅 상호작용 + 지역별 스냅 페이지</t>
+          <t xml:space="preserve">[TNSM-99] [취소/중복-TNSM-98] GlobalExceptionHandler 스코프 확장 *</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">미배정</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W35" s="14" t="n"/>
-      <c r="AC35" s="7" t="n"/>
+          <t xml:space="preserve">취소</t>
+        </is>
+      </c>
+      <c r="BD35" s="7"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P4</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>지역 이름 트리 도입 + 지역 매핑 단일화</t>
+          <t xml:space="preserve">[TNSM-26] 최종 QA · 배포/시연 환경 점검 · 하위 2건 중 완료 0</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W36" s="14" t="n"/>
-      <c r="AC36" s="7" t="n"/>
+          <t xml:space="preserve">진행 중(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AW36" s="18"/>
+      <c r="AX36" s="18"/>
+      <c r="BD36" s="7"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>P1-마이페이지</t>
+          <t xml:space="preserve">P4</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>내 여행(my_trips) 도입 + 라우트 분리 + 데모 시드 통합</t>
+          <t xml:space="preserve">[TNSM-27] 발표 리허설</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>김민규</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W37" s="14" t="n"/>
-      <c r="AC37" s="7" t="n"/>
+          <t xml:space="preserve">할 일(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AY37" s="16"/>
+      <c r="BD37" s="7"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>P1-통합</t>
+          <t xml:space="preserve">P4</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>개발 산출물 문서 작성(기획서/요구사항/화면설계/ERD 초안)</t>
+          <t xml:space="preserve">[TNSM-28] 최종 제출 · 하위 3건 중 완료 0</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>허수연</t>
+          <t xml:space="preserve">허수연</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="V38" s="14" t="n"/>
-      <c r="AC38" s="7" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>P1-통합</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>로컬 개발 환경 세팅 안내 문서화(이메일인증/소셜로그인)</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>허수연</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="X39" s="14" t="n"/>
-      <c r="AC39" s="7" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>P1-통합</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>데모 시드 스크립트 정리 및 재실행 버그 수정</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>허수연</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="W40" s="14" t="n"/>
-      <c r="AC40" s="7" t="n"/>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>AI 동선 최적화(RTE) — 좌표 기반 최근접 이웃 정렬 구현</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>허수연</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC41" s="7" t="n"/>
-      <c r="AD41" s="16" t="n"/>
-      <c r="AE41" s="16" t="n"/>
-      <c r="AF41" s="16" t="n"/>
-      <c r="AG41" s="16" t="n"/>
-      <c r="AH41" s="16" t="n"/>
-      <c r="AI41" s="16" t="n"/>
-      <c r="AJ41" s="16" t="n"/>
-      <c r="AK41" s="16" t="n"/>
-      <c r="AL41" s="16" t="n"/>
-      <c r="AM41" s="16" t="n"/>
-      <c r="AN41" s="16" t="n"/>
-      <c r="AO41" s="16" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>날씨 재추천/활동 이력 추천 고도화</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>이동인</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC42" s="7" t="n"/>
-      <c r="AD42" s="16" t="n"/>
-      <c r="AE42" s="16" t="n"/>
-      <c r="AF42" s="16" t="n"/>
-      <c r="AG42" s="16" t="n"/>
-      <c r="AH42" s="16" t="n"/>
-      <c r="AI42" s="16" t="n"/>
-      <c r="AJ42" s="16" t="n"/>
-      <c r="AK42" s="16" t="n"/>
-      <c r="AL42" s="16" t="n"/>
-      <c r="AM42" s="16" t="n"/>
-      <c r="AN42" s="16" t="n"/>
-      <c r="AO42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>히트맵·칭호 시스템 마감 + 역할 간 연동 안정화</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>김민규</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC43" s="7" t="n"/>
-      <c r="AD43" s="16" t="n"/>
-      <c r="AE43" s="16" t="n"/>
-      <c r="AF43" s="16" t="n"/>
-      <c r="AG43" s="16" t="n"/>
-      <c r="AH43" s="16" t="n"/>
-      <c r="AI43" s="16" t="n"/>
-      <c r="AJ43" s="16" t="n"/>
-      <c r="AK43" s="16" t="n"/>
-      <c r="AL43" s="16" t="n"/>
-      <c r="AM43" s="16" t="n"/>
-      <c r="AN43" s="16" t="n"/>
-      <c r="AO43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결제/예약 잔재 테이블 정리 (reservations 등 3종 + trip_schedules.reservation_id 제거, migration_v21). 조기 완료.</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>허수연</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
+          <t xml:space="preserve">할 일(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AZ38" s="16"/>
+      <c r="BD38" s="7"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">범례</t>
+        </is>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">완료</t>
         </is>
       </c>
-      <c r="AC44" s="7" t="n"/>
-      <c r="AI44" s="16" t="n"/>
-      <c r="AJ44" s="16" t="n"/>
-      <c r="AK44" s="16" t="n"/>
-      <c r="AL44" s="16" t="n"/>
-      <c r="AM44" s="16" t="n"/>
-      <c r="AN44" s="16" t="n"/>
-      <c r="AO44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>1차 통합 QA</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC45" s="7" t="n"/>
-      <c r="AM45" s="16" t="n"/>
-      <c r="AN45" s="16" t="n"/>
-      <c r="AO45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>전체 시나리오 통합 테스트 · 알려진 버그 수정</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC46" s="7" t="n"/>
-      <c r="AP46" s="16" t="n"/>
-      <c r="AQ46" s="16" t="n"/>
-      <c r="AR46" s="16" t="n"/>
-      <c r="AS46" s="16" t="n"/>
-      <c r="AT46" s="16" t="n"/>
-      <c r="AU46" s="16" t="n"/>
-      <c r="AV46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>최종 QA · 시연 환경 점검 · 발표 리허설 · 제출</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="AC47" s="7" t="n"/>
-      <c r="AW47" s="16" t="n"/>
-      <c r="AX47" s="16" t="n"/>
-      <c r="AY47" s="16" t="n"/>
-      <c r="AZ47" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>범례</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="n"/>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>완료(실적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>부분완료/진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>계획(예정) — 붉은 세로선 = 오늘(9/8)</t>
+    </row>
+    <row r="42">
+      <c r="B42" s="18"/>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="16"/>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">할 일(예정) — 붉은 세로선 = 오늘(10/5). 취소 업무는 막대 없음</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="G7:U7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A7:A8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:U7"/>
     <mergeCell ref="V7:AY7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="AZ7"/>
+    <mergeCell ref="AZ7:BI7"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>

--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -1735,38 +1735,38 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">할 일</t>
-        </is>
-      </c>
-      <c r="AG29" s="16"/>
-      <c r="AH29" s="16"/>
-      <c r="AI29" s="16"/>
-      <c r="AJ29" s="16"/>
-      <c r="AK29" s="16"/>
-      <c r="AL29" s="16"/>
-      <c r="AM29" s="16"/>
-      <c r="AN29" s="16"/>
-      <c r="AO29" s="16"/>
-      <c r="AP29" s="16"/>
-      <c r="AQ29" s="16"/>
-      <c r="AR29" s="16"/>
-      <c r="AS29" s="16"/>
-      <c r="AT29" s="16"/>
-      <c r="AU29" s="16"/>
-      <c r="AV29" s="16"/>
-      <c r="AW29" s="16"/>
-      <c r="AX29" s="16"/>
-      <c r="AY29" s="16"/>
-      <c r="AZ29" s="16"/>
-      <c r="BA29" s="16"/>
-      <c r="BB29" s="16"/>
-      <c r="BC29" s="16"/>
-      <c r="BD29" s="19"/>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="AG29" s="14"/>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="14"/>
+      <c r="AJ29" s="14"/>
+      <c r="AK29" s="14"/>
+      <c r="AL29" s="14"/>
+      <c r="AM29" s="14"/>
+      <c r="AN29" s="14"/>
+      <c r="AO29" s="14"/>
+      <c r="AP29" s="14"/>
+      <c r="AQ29" s="14"/>
+      <c r="AR29" s="14"/>
+      <c r="AS29" s="14"/>
+      <c r="AT29" s="14"/>
+      <c r="AU29" s="14"/>
+      <c r="AV29" s="14"/>
+      <c r="AW29" s="14"/>
+      <c r="AX29" s="14"/>
+      <c r="AY29" s="14"/>
+      <c r="AZ29" s="14"/>
+      <c r="BA29" s="14"/>
+      <c r="BB29" s="14"/>
+      <c r="BC29" s="14"/>
+      <c r="BD29" s="15"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -1796,13 +1796,13 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">할 일(기한 경과)</t>
-        </is>
-      </c>
-      <c r="AP30" s="16"/>
-      <c r="AQ30" s="16"/>
-      <c r="AR30" s="16"/>
-      <c r="AS30" s="16"/>
+          <t xml:space="preserve">진행 중(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AP30" s="18"/>
+      <c r="AQ30" s="18"/>
+      <c r="AR30" s="18"/>
+      <c r="AS30" s="18"/>
       <c r="BD30" s="7"/>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">할 일(기한 경과)</t>
-        </is>
-      </c>
-      <c r="AT32" s="16"/>
-      <c r="AU32" s="16"/>
-      <c r="AV32" s="16"/>
+          <t xml:space="preserve">진행 중(기한 경과)</t>
+        </is>
+      </c>
+      <c r="AT32" s="18"/>
+      <c r="AU32" s="18"/>
+      <c r="AV32" s="18"/>
       <c r="BD32" s="7"/>
     </row>
     <row r="33" ht="28" customHeight="1">

--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BI43"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2093,30 +2093,63 @@
       <c r="AZ38" s="16"/>
       <c r="BD38" s="7"/>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P4</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[TNSM-102] 시연 전 버그 수정 · 개선 (2026-10-05) · 하위 6건 중 완료 6</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">허수연</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-05</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-05</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="BD39" s="15"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">범례</t>
         </is>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18"/>
+      <c r="B42" s="14"/>
       <c r="C42" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="18"/>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">진행 중</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="16"/>
-      <c r="C43" s="17" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="16"/>
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">할 일(예정) — 붉은 세로선 = 오늘(10/5). 취소 업무는 막대 없음</t>
         </is>

--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="589">
   <si>
     <t>Project</t>
   </si>
@@ -547,7 +547,7 @@
     <t>완료 · 조기 완료(09-12) · 1차 통합 QA 결과</t>
   </si>
   <si>
-    <t>4.0 통합 테스트 · 버그 수정 (P3)   [TNSM-4]  09-21 ~ 09-27  ·  진행 중</t>
+    <t>4.0 통합 테스트 · 버그 수정 (P3)   [TNSM-4]  09-21 ~ 10-07  ·  완료</t>
   </si>
   <si>
     <t>/mypage 500 — TitleService.allTitlesOrdered() NPE (category NULL 칭호)</t>
@@ -583,102 +583,99 @@
     <t>2026-09-21</t>
   </si>
   <si>
-    <t>진행 중(기한 09-24 경과)</t>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>전체 시나리오 플로우 점검(번개모임→채팅→계획표)  [TNSM-69]</t>
   </si>
   <si>
+    <t>기존 알려진 버그 수정(플래너 리사이즈/삭제 등)  [TNSM-70]</t>
+  </si>
+  <si>
+    <t>P2 기능 (선택)</t>
+  </si>
+  <si>
+    <t>[TNSM-24]</t>
+  </si>
+  <si>
+    <t>등급 표시  [TNSM-71]</t>
+  </si>
+  <si>
+    <t>정산 잔돈 재미 요소  [TNSM-72]</t>
+  </si>
+  <si>
+    <t>마이페이지 PDF 영수증  [TNSM-73]</t>
+  </si>
+  <si>
+    <t>발표자료 · 데모 시나리오 준비</t>
+  </si>
+  <si>
+    <t>[TNSM-25]</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>완료 · 발표 PPT·시연 대본(docs/06)</t>
+  </si>
+  <si>
+    <t>발표 슬라이드 제작  [TNSM-74]</t>
+  </si>
+  <si>
+    <t>시연 시나리오·계정 준비  [TNSM-75]</t>
+  </si>
+  <si>
+    <t>5.0 최종 마무리 (P4)   [TNSM-5]  09-28 ~ 10-16  ·  진행 중</t>
+  </si>
+  <si>
+    <t>최종 QA · 배포/시연 환경 점검</t>
+  </si>
+  <si>
+    <t>[TNSM-26]</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>완료 · 시연 가이드(docs/05)</t>
+  </si>
+  <si>
+    <t>운영/시연 서버 점검  [TNSM-76]</t>
+  </si>
+  <si>
+    <t>최종 회귀 테스트  [TNSM-77]</t>
+  </si>
+  <si>
+    <t>발표 리허설</t>
+  </si>
+  <si>
+    <t>[TNSM-27]</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>최종 제출</t>
+  </si>
+  <si>
+    <t>[TNSM-28]</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>할 일 · 제출 산출물 일체</t>
+  </si>
+  <si>
+    <t>제안서 최종본 제출  [TNSM-78]</t>
+  </si>
+  <si>
     <t>할 일</t>
   </si>
   <si>
-    <t>기존 알려진 버그 수정(플래너 리사이즈/삭제 등)  [TNSM-70]</t>
-  </si>
-  <si>
-    <t>P2 기능 (선택)</t>
-  </si>
-  <si>
-    <t>[TNSM-24]</t>
-  </si>
-  <si>
-    <t>등급 표시  [TNSM-71]</t>
-  </si>
-  <si>
-    <t>정산 잔돈 재미 요소  [TNSM-72]</t>
-  </si>
-  <si>
-    <t>마이페이지 PDF 영수증  [TNSM-73]</t>
-  </si>
-  <si>
-    <t>발표자료 · 데모 시나리오 준비</t>
-  </si>
-  <si>
-    <t>[TNSM-25]</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>진행 중(기한 09-27 경과) · 발표 PPT·시연 대본(docs/06)</t>
-  </si>
-  <si>
-    <t>발표 슬라이드 제작  [TNSM-74]</t>
-  </si>
-  <si>
-    <t>시연 시나리오·계정 준비  [TNSM-75]</t>
-  </si>
-  <si>
-    <t>진행 중</t>
-  </si>
-  <si>
-    <t>5.0 최종 마무리 (P4)   [TNSM-5]  09-28 ~ 10-01  ·  진행 중</t>
-  </si>
-  <si>
-    <t>최종 QA · 배포/시연 환경 점검</t>
-  </si>
-  <si>
-    <t>[TNSM-26]</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
-  </si>
-  <si>
-    <t>진행 중(기한 09-29 경과) · 시연 가이드(docs/05)</t>
-  </si>
-  <si>
-    <t>운영/시연 서버 점검  [TNSM-76]</t>
-  </si>
-  <si>
-    <t>최종 회귀 테스트  [TNSM-77]</t>
-  </si>
-  <si>
-    <t>발표 리허설</t>
-  </si>
-  <si>
-    <t>[TNSM-27]</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>할 일(기한 09-30 경과)</t>
-  </si>
-  <si>
-    <t>최종 제출</t>
-  </si>
-  <si>
-    <t>[TNSM-28]</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>할 일(기한 10-01 경과) · 제출 산출물 일체</t>
-  </si>
-  <si>
-    <t>제안서 최종본 제출  [TNSM-78]</t>
-  </si>
-  <si>
     <t>소스코드 최종 제출  [TNSM-79]</t>
   </si>
   <si>
@@ -730,9 +727,6 @@
     <t>계획표 AI 검증 반영(v26) · 팀 채팅 탭 · Gemini 번역 · WebClient 공통화</t>
   </si>
   <si>
-    <t>2026-10-07</t>
-  </si>
-  <si>
     <t>완료 · PR #100·#103·#105·#113·#114</t>
   </si>
   <si>
@@ -778,10 +772,10 @@
     <t>※ 소요 기간(초록)은 기한 안에서 실제 진행한 기간, 초과 기간(주황)은 기한을 넘겨 진행한 기간(진행 중·할 일은 오늘까지). 취소 업무는 줄긋기, 막대 없음.</t>
   </si>
   <si>
-    <t>※ Jira 해결일이 일괄 정리일(09-05, 09-12)인 업무는 실제 완료일이 아니라서 기한 내 완료로 표시했다. 10/5 이후 작업은 Jira 에 등록되지 않아 git 커밋·PR 기준으로 추가했다.</t>
-  </si>
-  <si>
-    <t>※ TNSM-25~28(발표자료·리허설·최종 제출)은 Jira 기한(9/27~10/1)이 지나 초과로 표시된다 — 실제 발표일에 맞춰 Jira 기한을 갱신하면 이 공정도도 다시 뽑을 수 있다.</t>
+    <t>※ Jira 해결일이 일괄 정리일(09-05, 09-12, 10-15)인 업무는 실제 완료일이 아니라서 기한 내 완료로 표시했다. 10/5 이후 작업은 Jira 에 등록되지 않아 git 커밋·PR 기준으로 추가했다.</t>
+  </si>
+  <si>
+    <t>※ 발표(10/7) 후 Jira 기한을 실제 일정에 맞춰 갱신함(2026-10-15): 통합 테스트·발표 준비·최종 QA·리허설 기한 10/7, 최종 제출 기한 10/16.</t>
   </si>
   <si>
     <t>6.0 웹페이지 제작 — 기능 체크리스트 (02_요구사항정의서 기준, 2026-10-15 main)</t>
@@ -2022,7 +2016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2092,7 +2086,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10009,10 +10002,10 @@
         <v>189</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>190</v>
+        <v>43</v>
       </c>
       <c r="J89" s="20"/>
       <c r="K89" s="20"/>
@@ -10046,27 +10039,27 @@
       <c r="AM89" s="19"/>
       <c r="AN89" s="19"/>
       <c r="AO89" s="19"/>
-      <c r="AP89" s="30"/>
-      <c r="AQ89" s="30"/>
-      <c r="AR89" s="30"/>
-      <c r="AS89" s="30"/>
-      <c r="AT89" s="30"/>
-      <c r="AU89" s="30"/>
-      <c r="AV89" s="30"/>
-      <c r="AW89" s="30"/>
-      <c r="AX89" s="30"/>
-      <c r="AY89" s="30"/>
-      <c r="AZ89" s="30"/>
-      <c r="BA89" s="30"/>
-      <c r="BB89" s="30"/>
-      <c r="BC89" s="30"/>
-      <c r="BD89" s="30"/>
-      <c r="BE89" s="30"/>
-      <c r="BF89" s="30"/>
-      <c r="BG89" s="30"/>
-      <c r="BH89" s="30"/>
-      <c r="BI89" s="30"/>
-      <c r="BJ89" s="31"/>
+      <c r="AP89" s="19"/>
+      <c r="AQ89" s="19"/>
+      <c r="AR89" s="19"/>
+      <c r="AS89" s="19"/>
+      <c r="AT89" s="19"/>
+      <c r="AU89" s="19"/>
+      <c r="AV89" s="19"/>
+      <c r="AW89" s="19"/>
+      <c r="AX89" s="19"/>
+      <c r="AY89" s="19"/>
+      <c r="AZ89" s="19"/>
+      <c r="BA89" s="19"/>
+      <c r="BB89" s="19"/>
+      <c r="BC89" s="20"/>
+      <c r="BD89" s="20"/>
+      <c r="BE89" s="21"/>
+      <c r="BF89" s="21"/>
+      <c r="BG89" s="20"/>
+      <c r="BH89" s="20"/>
+      <c r="BI89" s="20"/>
+      <c r="BJ89" s="22"/>
       <c r="BK89" s="20"/>
       <c r="BL89" s="21"/>
       <c r="BM89" s="21"/>
@@ -10093,10 +10086,10 @@
         <v>189</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I90" s="25" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="J90" s="20"/>
       <c r="K90" s="20"/>
@@ -10130,27 +10123,27 @@
       <c r="AM90" s="19"/>
       <c r="AN90" s="19"/>
       <c r="AO90" s="19"/>
-      <c r="AP90" s="30"/>
-      <c r="AQ90" s="30"/>
-      <c r="AR90" s="30"/>
-      <c r="AS90" s="30"/>
-      <c r="AT90" s="30"/>
-      <c r="AU90" s="30"/>
-      <c r="AV90" s="30"/>
-      <c r="AW90" s="30"/>
-      <c r="AX90" s="30"/>
-      <c r="AY90" s="30"/>
-      <c r="AZ90" s="30"/>
-      <c r="BA90" s="30"/>
-      <c r="BB90" s="30"/>
-      <c r="BC90" s="30"/>
-      <c r="BD90" s="30"/>
-      <c r="BE90" s="30"/>
-      <c r="BF90" s="30"/>
-      <c r="BG90" s="30"/>
-      <c r="BH90" s="30"/>
-      <c r="BI90" s="30"/>
-      <c r="BJ90" s="31"/>
+      <c r="AP90" s="19"/>
+      <c r="AQ90" s="19"/>
+      <c r="AR90" s="19"/>
+      <c r="AS90" s="19"/>
+      <c r="AT90" s="19"/>
+      <c r="AU90" s="19"/>
+      <c r="AV90" s="19"/>
+      <c r="AW90" s="19"/>
+      <c r="AX90" s="19"/>
+      <c r="AY90" s="19"/>
+      <c r="AZ90" s="19"/>
+      <c r="BA90" s="19"/>
+      <c r="BB90" s="19"/>
+      <c r="BC90" s="20"/>
+      <c r="BD90" s="20"/>
+      <c r="BE90" s="21"/>
+      <c r="BF90" s="21"/>
+      <c r="BG90" s="20"/>
+      <c r="BH90" s="20"/>
+      <c r="BI90" s="20"/>
+      <c r="BJ90" s="22"/>
       <c r="BK90" s="20"/>
       <c r="BL90" s="21"/>
       <c r="BM90" s="21"/>
@@ -10167,7 +10160,7 @@
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E91" s="23"/>
       <c r="F91" s="24" t="s">
@@ -10177,7 +10170,7 @@
         <v>189</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I91" s="25" t="s">
         <v>43</v>
@@ -10214,27 +10207,27 @@
       <c r="AM91" s="19"/>
       <c r="AN91" s="19"/>
       <c r="AO91" s="19"/>
-      <c r="AP91" s="30"/>
-      <c r="AQ91" s="30"/>
-      <c r="AR91" s="30"/>
-      <c r="AS91" s="30"/>
-      <c r="AT91" s="30"/>
-      <c r="AU91" s="30"/>
-      <c r="AV91" s="30"/>
-      <c r="AW91" s="30"/>
-      <c r="AX91" s="30"/>
-      <c r="AY91" s="30"/>
-      <c r="AZ91" s="30"/>
-      <c r="BA91" s="30"/>
-      <c r="BB91" s="30"/>
-      <c r="BC91" s="30"/>
-      <c r="BD91" s="30"/>
-      <c r="BE91" s="30"/>
-      <c r="BF91" s="30"/>
-      <c r="BG91" s="30"/>
-      <c r="BH91" s="30"/>
-      <c r="BI91" s="30"/>
-      <c r="BJ91" s="31"/>
+      <c r="AP91" s="19"/>
+      <c r="AQ91" s="19"/>
+      <c r="AR91" s="19"/>
+      <c r="AS91" s="19"/>
+      <c r="AT91" s="19"/>
+      <c r="AU91" s="19"/>
+      <c r="AV91" s="19"/>
+      <c r="AW91" s="19"/>
+      <c r="AX91" s="19"/>
+      <c r="AY91" s="19"/>
+      <c r="AZ91" s="19"/>
+      <c r="BA91" s="19"/>
+      <c r="BB91" s="19"/>
+      <c r="BC91" s="20"/>
+      <c r="BD91" s="20"/>
+      <c r="BE91" s="21"/>
+      <c r="BF91" s="21"/>
+      <c r="BG91" s="20"/>
+      <c r="BH91" s="20"/>
+      <c r="BI91" s="20"/>
+      <c r="BJ91" s="22"/>
       <c r="BK91" s="20"/>
       <c r="BL91" s="21"/>
       <c r="BM91" s="21"/>
@@ -10252,10 +10245,10 @@
         <v>5</v>
       </c>
       <c r="C92" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="D92" s="28" t="s">
         <v>194</v>
-      </c>
-      <c r="D92" s="28" t="s">
-        <v>195</v>
       </c>
       <c r="E92" s="28"/>
       <c r="F92" s="26" t="s">
@@ -10339,7 +10332,7 @@
       <c r="B93" s="26"/>
       <c r="C93" s="27"/>
       <c r="D93" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="26" t="s">
@@ -10423,7 +10416,7 @@
       <c r="B94" s="26"/>
       <c r="C94" s="27"/>
       <c r="D94" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="26" t="s">
@@ -10507,7 +10500,7 @@
       <c r="B95" s="26"/>
       <c r="C95" s="27"/>
       <c r="D95" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="26" t="s">
@@ -10592,23 +10585,23 @@
         <v>6</v>
       </c>
       <c r="C96" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D96" s="16" t="s">
         <v>199</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="E96" s="16"/>
       <c r="F96" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G96" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="H96" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="I96" s="18" t="s">
         <v>201</v>
-      </c>
-      <c r="H96" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="I96" s="18" t="s">
-        <v>202</v>
       </c>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -10645,24 +10638,24 @@
       <c r="AP96" s="19"/>
       <c r="AQ96" s="19"/>
       <c r="AR96" s="19"/>
-      <c r="AS96" s="30"/>
-      <c r="AT96" s="30"/>
-      <c r="AU96" s="30"/>
-      <c r="AV96" s="30"/>
-      <c r="AW96" s="30"/>
-      <c r="AX96" s="30"/>
-      <c r="AY96" s="30"/>
-      <c r="AZ96" s="30"/>
-      <c r="BA96" s="30"/>
-      <c r="BB96" s="30"/>
-      <c r="BC96" s="30"/>
-      <c r="BD96" s="30"/>
-      <c r="BE96" s="30"/>
-      <c r="BF96" s="30"/>
-      <c r="BG96" s="30"/>
-      <c r="BH96" s="30"/>
-      <c r="BI96" s="30"/>
-      <c r="BJ96" s="31"/>
+      <c r="AS96" s="19"/>
+      <c r="AT96" s="19"/>
+      <c r="AU96" s="19"/>
+      <c r="AV96" s="19"/>
+      <c r="AW96" s="19"/>
+      <c r="AX96" s="19"/>
+      <c r="AY96" s="19"/>
+      <c r="AZ96" s="19"/>
+      <c r="BA96" s="19"/>
+      <c r="BB96" s="19"/>
+      <c r="BC96" s="20"/>
+      <c r="BD96" s="20"/>
+      <c r="BE96" s="21"/>
+      <c r="BF96" s="21"/>
+      <c r="BG96" s="20"/>
+      <c r="BH96" s="20"/>
+      <c r="BI96" s="20"/>
+      <c r="BJ96" s="22"/>
       <c r="BK96" s="20"/>
       <c r="BL96" s="21"/>
       <c r="BM96" s="21"/>
@@ -10679,20 +10672,20 @@
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E97" s="23"/>
       <c r="F97" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -10729,24 +10722,24 @@
       <c r="AP97" s="19"/>
       <c r="AQ97" s="19"/>
       <c r="AR97" s="19"/>
-      <c r="AS97" s="30"/>
-      <c r="AT97" s="30"/>
-      <c r="AU97" s="30"/>
-      <c r="AV97" s="30"/>
-      <c r="AW97" s="30"/>
-      <c r="AX97" s="30"/>
-      <c r="AY97" s="30"/>
-      <c r="AZ97" s="30"/>
-      <c r="BA97" s="30"/>
-      <c r="BB97" s="30"/>
-      <c r="BC97" s="30"/>
-      <c r="BD97" s="30"/>
-      <c r="BE97" s="30"/>
-      <c r="BF97" s="30"/>
-      <c r="BG97" s="30"/>
-      <c r="BH97" s="30"/>
-      <c r="BI97" s="30"/>
-      <c r="BJ97" s="31"/>
+      <c r="AS97" s="19"/>
+      <c r="AT97" s="19"/>
+      <c r="AU97" s="19"/>
+      <c r="AV97" s="19"/>
+      <c r="AW97" s="19"/>
+      <c r="AX97" s="19"/>
+      <c r="AY97" s="19"/>
+      <c r="AZ97" s="19"/>
+      <c r="BA97" s="19"/>
+      <c r="BB97" s="19"/>
+      <c r="BC97" s="20"/>
+      <c r="BD97" s="20"/>
+      <c r="BE97" s="21"/>
+      <c r="BF97" s="21"/>
+      <c r="BG97" s="20"/>
+      <c r="BH97" s="20"/>
+      <c r="BI97" s="20"/>
+      <c r="BJ97" s="22"/>
       <c r="BK97" s="20"/>
       <c r="BL97" s="21"/>
       <c r="BM97" s="21"/>
@@ -10763,20 +10756,20 @@
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I98" s="25" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -10813,24 +10806,24 @@
       <c r="AP98" s="19"/>
       <c r="AQ98" s="19"/>
       <c r="AR98" s="19"/>
-      <c r="AS98" s="30"/>
-      <c r="AT98" s="30"/>
-      <c r="AU98" s="30"/>
-      <c r="AV98" s="30"/>
-      <c r="AW98" s="30"/>
-      <c r="AX98" s="30"/>
-      <c r="AY98" s="30"/>
-      <c r="AZ98" s="30"/>
-      <c r="BA98" s="30"/>
-      <c r="BB98" s="30"/>
-      <c r="BC98" s="30"/>
-      <c r="BD98" s="30"/>
-      <c r="BE98" s="30"/>
-      <c r="BF98" s="30"/>
-      <c r="BG98" s="30"/>
-      <c r="BH98" s="30"/>
-      <c r="BI98" s="30"/>
-      <c r="BJ98" s="31"/>
+      <c r="AS98" s="19"/>
+      <c r="AT98" s="19"/>
+      <c r="AU98" s="19"/>
+      <c r="AV98" s="19"/>
+      <c r="AW98" s="19"/>
+      <c r="AX98" s="19"/>
+      <c r="AY98" s="19"/>
+      <c r="AZ98" s="19"/>
+      <c r="BA98" s="19"/>
+      <c r="BB98" s="19"/>
+      <c r="BC98" s="20"/>
+      <c r="BD98" s="20"/>
+      <c r="BE98" s="21"/>
+      <c r="BF98" s="21"/>
+      <c r="BG98" s="20"/>
+      <c r="BH98" s="20"/>
+      <c r="BI98" s="20"/>
+      <c r="BJ98" s="22"/>
       <c r="BK98" s="20"/>
       <c r="BL98" s="21"/>
       <c r="BM98" s="21"/>
@@ -10844,7 +10837,7 @@
     </row>
     <row r="99" ht="16" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -10924,23 +10917,23 @@
         <v>1</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E100" s="16"/>
       <c r="F100" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -10979,22 +10972,22 @@
       <c r="AR100" s="21"/>
       <c r="AS100" s="19"/>
       <c r="AT100" s="19"/>
-      <c r="AU100" s="30"/>
-      <c r="AV100" s="30"/>
-      <c r="AW100" s="30"/>
-      <c r="AX100" s="30"/>
-      <c r="AY100" s="30"/>
-      <c r="AZ100" s="30"/>
-      <c r="BA100" s="30"/>
-      <c r="BB100" s="30"/>
-      <c r="BC100" s="30"/>
-      <c r="BD100" s="30"/>
-      <c r="BE100" s="30"/>
-      <c r="BF100" s="30"/>
-      <c r="BG100" s="30"/>
-      <c r="BH100" s="30"/>
-      <c r="BI100" s="30"/>
-      <c r="BJ100" s="31"/>
+      <c r="AU100" s="19"/>
+      <c r="AV100" s="19"/>
+      <c r="AW100" s="19"/>
+      <c r="AX100" s="19"/>
+      <c r="AY100" s="19"/>
+      <c r="AZ100" s="19"/>
+      <c r="BA100" s="19"/>
+      <c r="BB100" s="19"/>
+      <c r="BC100" s="20"/>
+      <c r="BD100" s="20"/>
+      <c r="BE100" s="21"/>
+      <c r="BF100" s="21"/>
+      <c r="BG100" s="20"/>
+      <c r="BH100" s="20"/>
+      <c r="BI100" s="20"/>
+      <c r="BJ100" s="22"/>
       <c r="BK100" s="20"/>
       <c r="BL100" s="21"/>
       <c r="BM100" s="21"/>
@@ -11011,20 +11004,20 @@
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I101" s="25" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -11063,22 +11056,22 @@
       <c r="AR101" s="21"/>
       <c r="AS101" s="19"/>
       <c r="AT101" s="19"/>
-      <c r="AU101" s="30"/>
-      <c r="AV101" s="30"/>
-      <c r="AW101" s="30"/>
-      <c r="AX101" s="30"/>
-      <c r="AY101" s="30"/>
-      <c r="AZ101" s="30"/>
-      <c r="BA101" s="30"/>
-      <c r="BB101" s="30"/>
-      <c r="BC101" s="30"/>
-      <c r="BD101" s="30"/>
-      <c r="BE101" s="30"/>
-      <c r="BF101" s="30"/>
-      <c r="BG101" s="30"/>
-      <c r="BH101" s="30"/>
-      <c r="BI101" s="30"/>
-      <c r="BJ101" s="31"/>
+      <c r="AU101" s="19"/>
+      <c r="AV101" s="19"/>
+      <c r="AW101" s="19"/>
+      <c r="AX101" s="19"/>
+      <c r="AY101" s="19"/>
+      <c r="AZ101" s="19"/>
+      <c r="BA101" s="19"/>
+      <c r="BB101" s="19"/>
+      <c r="BC101" s="20"/>
+      <c r="BD101" s="20"/>
+      <c r="BE101" s="21"/>
+      <c r="BF101" s="21"/>
+      <c r="BG101" s="20"/>
+      <c r="BH101" s="20"/>
+      <c r="BI101" s="20"/>
+      <c r="BJ101" s="22"/>
       <c r="BK101" s="20"/>
       <c r="BL101" s="21"/>
       <c r="BM101" s="21"/>
@@ -11095,20 +11088,20 @@
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I102" s="25" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -11147,22 +11140,22 @@
       <c r="AR102" s="21"/>
       <c r="AS102" s="19"/>
       <c r="AT102" s="19"/>
-      <c r="AU102" s="30"/>
-      <c r="AV102" s="30"/>
-      <c r="AW102" s="30"/>
-      <c r="AX102" s="30"/>
-      <c r="AY102" s="30"/>
-      <c r="AZ102" s="30"/>
-      <c r="BA102" s="30"/>
-      <c r="BB102" s="30"/>
-      <c r="BC102" s="30"/>
-      <c r="BD102" s="30"/>
-      <c r="BE102" s="30"/>
-      <c r="BF102" s="30"/>
-      <c r="BG102" s="30"/>
-      <c r="BH102" s="30"/>
-      <c r="BI102" s="30"/>
-      <c r="BJ102" s="31"/>
+      <c r="AU102" s="19"/>
+      <c r="AV102" s="19"/>
+      <c r="AW102" s="19"/>
+      <c r="AX102" s="19"/>
+      <c r="AY102" s="19"/>
+      <c r="AZ102" s="19"/>
+      <c r="BA102" s="19"/>
+      <c r="BB102" s="19"/>
+      <c r="BC102" s="20"/>
+      <c r="BD102" s="20"/>
+      <c r="BE102" s="21"/>
+      <c r="BF102" s="21"/>
+      <c r="BG102" s="20"/>
+      <c r="BH102" s="20"/>
+      <c r="BI102" s="20"/>
+      <c r="BJ102" s="22"/>
       <c r="BK102" s="20"/>
       <c r="BL102" s="21"/>
       <c r="BM102" s="21"/>
@@ -11180,23 +11173,23 @@
         <v>2</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E103" s="16"/>
       <c r="F103" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="I103" s="18" t="s">
-        <v>216</v>
+        <v>43</v>
       </c>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -11236,21 +11229,21 @@
       <c r="AS103" s="20"/>
       <c r="AT103" s="20"/>
       <c r="AU103" s="19"/>
-      <c r="AV103" s="30"/>
-      <c r="AW103" s="30"/>
-      <c r="AX103" s="30"/>
-      <c r="AY103" s="30"/>
-      <c r="AZ103" s="30"/>
-      <c r="BA103" s="30"/>
-      <c r="BB103" s="30"/>
-      <c r="BC103" s="30"/>
-      <c r="BD103" s="30"/>
-      <c r="BE103" s="30"/>
-      <c r="BF103" s="30"/>
-      <c r="BG103" s="30"/>
-      <c r="BH103" s="30"/>
-      <c r="BI103" s="30"/>
-      <c r="BJ103" s="31"/>
+      <c r="AV103" s="19"/>
+      <c r="AW103" s="19"/>
+      <c r="AX103" s="19"/>
+      <c r="AY103" s="19"/>
+      <c r="AZ103" s="19"/>
+      <c r="BA103" s="19"/>
+      <c r="BB103" s="19"/>
+      <c r="BC103" s="20"/>
+      <c r="BD103" s="20"/>
+      <c r="BE103" s="21"/>
+      <c r="BF103" s="21"/>
+      <c r="BG103" s="20"/>
+      <c r="BH103" s="20"/>
+      <c r="BI103" s="20"/>
+      <c r="BJ103" s="22"/>
       <c r="BK103" s="20"/>
       <c r="BL103" s="21"/>
       <c r="BM103" s="21"/>
@@ -11262,29 +11255,29 @@
       <c r="BS103" s="21"/>
       <c r="BT103" s="21"/>
     </row>
-    <row r="104" ht="34" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="104" ht="20" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="17">
         <v>3</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E104" s="16"/>
       <c r="F104" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -11325,21 +11318,21 @@
       <c r="AT104" s="20"/>
       <c r="AU104" s="20"/>
       <c r="AV104" s="19"/>
-      <c r="AW104" s="30"/>
-      <c r="AX104" s="30"/>
-      <c r="AY104" s="30"/>
-      <c r="AZ104" s="30"/>
-      <c r="BA104" s="30"/>
-      <c r="BB104" s="30"/>
-      <c r="BC104" s="30"/>
-      <c r="BD104" s="30"/>
-      <c r="BE104" s="30"/>
-      <c r="BF104" s="30"/>
-      <c r="BG104" s="30"/>
-      <c r="BH104" s="30"/>
-      <c r="BI104" s="30"/>
+      <c r="AW104" s="19"/>
+      <c r="AX104" s="19"/>
+      <c r="AY104" s="19"/>
+      <c r="AZ104" s="19"/>
+      <c r="BA104" s="19"/>
+      <c r="BB104" s="19"/>
+      <c r="BC104" s="19"/>
+      <c r="BD104" s="19"/>
+      <c r="BE104" s="19"/>
+      <c r="BF104" s="19"/>
+      <c r="BG104" s="19"/>
+      <c r="BH104" s="19"/>
+      <c r="BI104" s="19"/>
       <c r="BJ104" s="31"/>
-      <c r="BK104" s="20"/>
+      <c r="BK104" s="29"/>
       <c r="BL104" s="21"/>
       <c r="BM104" s="21"/>
       <c r="BN104" s="20"/>
@@ -11355,20 +11348,20 @@
       <c r="B105" s="24"/>
       <c r="C105" s="25"/>
       <c r="D105" s="23" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G105" s="24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H105" s="24" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="I105" s="25" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="J105" s="20"/>
       <c r="K105" s="20"/>
@@ -11409,21 +11402,21 @@
       <c r="AT105" s="20"/>
       <c r="AU105" s="20"/>
       <c r="AV105" s="19"/>
-      <c r="AW105" s="30"/>
-      <c r="AX105" s="30"/>
-      <c r="AY105" s="30"/>
-      <c r="AZ105" s="30"/>
-      <c r="BA105" s="30"/>
-      <c r="BB105" s="30"/>
-      <c r="BC105" s="30"/>
-      <c r="BD105" s="30"/>
-      <c r="BE105" s="30"/>
-      <c r="BF105" s="30"/>
-      <c r="BG105" s="30"/>
-      <c r="BH105" s="30"/>
-      <c r="BI105" s="30"/>
+      <c r="AW105" s="19"/>
+      <c r="AX105" s="19"/>
+      <c r="AY105" s="19"/>
+      <c r="AZ105" s="19"/>
+      <c r="BA105" s="19"/>
+      <c r="BB105" s="19"/>
+      <c r="BC105" s="19"/>
+      <c r="BD105" s="19"/>
+      <c r="BE105" s="19"/>
+      <c r="BF105" s="19"/>
+      <c r="BG105" s="19"/>
+      <c r="BH105" s="19"/>
+      <c r="BI105" s="19"/>
       <c r="BJ105" s="31"/>
-      <c r="BK105" s="20"/>
+      <c r="BK105" s="29"/>
       <c r="BL105" s="21"/>
       <c r="BM105" s="21"/>
       <c r="BN105" s="20"/>
@@ -11439,20 +11432,20 @@
       <c r="B106" s="24"/>
       <c r="C106" s="25"/>
       <c r="D106" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G106" s="24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H106" s="24" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -11493,21 +11486,21 @@
       <c r="AT106" s="20"/>
       <c r="AU106" s="20"/>
       <c r="AV106" s="19"/>
-      <c r="AW106" s="30"/>
-      <c r="AX106" s="30"/>
-      <c r="AY106" s="30"/>
-      <c r="AZ106" s="30"/>
-      <c r="BA106" s="30"/>
-      <c r="BB106" s="30"/>
-      <c r="BC106" s="30"/>
-      <c r="BD106" s="30"/>
-      <c r="BE106" s="30"/>
-      <c r="BF106" s="30"/>
-      <c r="BG106" s="30"/>
-      <c r="BH106" s="30"/>
-      <c r="BI106" s="30"/>
+      <c r="AW106" s="19"/>
+      <c r="AX106" s="19"/>
+      <c r="AY106" s="19"/>
+      <c r="AZ106" s="19"/>
+      <c r="BA106" s="19"/>
+      <c r="BB106" s="19"/>
+      <c r="BC106" s="19"/>
+      <c r="BD106" s="19"/>
+      <c r="BE106" s="19"/>
+      <c r="BF106" s="19"/>
+      <c r="BG106" s="19"/>
+      <c r="BH106" s="19"/>
+      <c r="BI106" s="19"/>
       <c r="BJ106" s="31"/>
-      <c r="BK106" s="20"/>
+      <c r="BK106" s="29"/>
       <c r="BL106" s="21"/>
       <c r="BM106" s="21"/>
       <c r="BN106" s="20"/>
@@ -11523,20 +11516,20 @@
       <c r="B107" s="24"/>
       <c r="C107" s="25"/>
       <c r="D107" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G107" s="24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H107" s="24" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="I107" s="25" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -11577,21 +11570,21 @@
       <c r="AT107" s="20"/>
       <c r="AU107" s="20"/>
       <c r="AV107" s="19"/>
-      <c r="AW107" s="30"/>
-      <c r="AX107" s="30"/>
-      <c r="AY107" s="30"/>
-      <c r="AZ107" s="30"/>
-      <c r="BA107" s="30"/>
-      <c r="BB107" s="30"/>
-      <c r="BC107" s="30"/>
-      <c r="BD107" s="30"/>
-      <c r="BE107" s="30"/>
-      <c r="BF107" s="30"/>
-      <c r="BG107" s="30"/>
-      <c r="BH107" s="30"/>
-      <c r="BI107" s="30"/>
+      <c r="AW107" s="19"/>
+      <c r="AX107" s="19"/>
+      <c r="AY107" s="19"/>
+      <c r="AZ107" s="19"/>
+      <c r="BA107" s="19"/>
+      <c r="BB107" s="19"/>
+      <c r="BC107" s="19"/>
+      <c r="BD107" s="19"/>
+      <c r="BE107" s="19"/>
+      <c r="BF107" s="19"/>
+      <c r="BG107" s="19"/>
+      <c r="BH107" s="19"/>
+      <c r="BI107" s="19"/>
       <c r="BJ107" s="31"/>
-      <c r="BK107" s="20"/>
+      <c r="BK107" s="29"/>
       <c r="BL107" s="21"/>
       <c r="BM107" s="21"/>
       <c r="BN107" s="20"/>
@@ -11608,10 +11601,10 @@
         <v>4</v>
       </c>
       <c r="C108" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D108" s="16" t="s">
         <v>224</v>
-      </c>
-      <c r="D108" s="16" t="s">
-        <v>225</v>
       </c>
       <c r="E108" s="16"/>
       <c r="F108" s="17" t="s">
@@ -11695,7 +11688,7 @@
       <c r="B109" s="24"/>
       <c r="C109" s="25"/>
       <c r="D109" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="24" t="s">
@@ -11779,7 +11772,7 @@
       <c r="B110" s="24"/>
       <c r="C110" s="25"/>
       <c r="D110" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="24" t="s">
@@ -11863,7 +11856,7 @@
       <c r="B111" s="24"/>
       <c r="C111" s="25"/>
       <c r="D111" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="24" t="s">
@@ -11947,7 +11940,7 @@
       <c r="B112" s="24"/>
       <c r="C112" s="25"/>
       <c r="D112" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="24" t="s">
@@ -12031,7 +12024,7 @@
       <c r="B113" s="24"/>
       <c r="C113" s="25"/>
       <c r="D113" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="24" t="s">
@@ -12115,7 +12108,7 @@
       <c r="B114" s="24"/>
       <c r="C114" s="25"/>
       <c r="D114" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="24" t="s">
@@ -12200,10 +12193,10 @@
         <v>5</v>
       </c>
       <c r="C115" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>232</v>
-      </c>
-      <c r="D115" s="16" t="s">
-        <v>233</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17" t="s">
@@ -12216,7 +12209,7 @@
         <v>148</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -12288,23 +12281,23 @@
         <v>6</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E116" s="16"/>
       <c r="F116" s="17" t="s">
         <v>107</v>
       </c>
       <c r="G116" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="H116" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="I116" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="H116" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="I116" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -12376,23 +12369,23 @@
         <v>7</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E117" s="16"/>
       <c r="F117" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H117" s="17" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -12464,23 +12457,23 @@
         <v>8</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E118" s="16"/>
       <c r="F118" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H118" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -12552,23 +12545,23 @@
         <v>9</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E119" s="16"/>
       <c r="F119" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="I119" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -12640,23 +12633,23 @@
         <v>10</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E120" s="16"/>
       <c r="F120" s="17" t="s">
         <v>88</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H120" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -12728,23 +12721,23 @@
         <v>11</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E121" s="16"/>
       <c r="F121" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I121" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -12816,10 +12809,10 @@
         <v>12</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E122" s="16"/>
       <c r="F122" s="17" t="s">
@@ -12832,7 +12825,7 @@
         <v>7</v>
       </c>
       <c r="I122" s="18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -12886,7 +12879,7 @@
       <c r="BG122" s="20"/>
       <c r="BH122" s="20"/>
       <c r="BI122" s="20"/>
-      <c r="BJ122" s="32"/>
+      <c r="BJ122" s="31"/>
       <c r="BK122" s="20"/>
       <c r="BL122" s="21"/>
       <c r="BM122" s="21"/>
@@ -12904,10 +12897,10 @@
         <v>13</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E123" s="16"/>
       <c r="F123" s="17" t="s">
@@ -12920,7 +12913,7 @@
         <v>7</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -12974,7 +12967,7 @@
       <c r="BG123" s="20"/>
       <c r="BH123" s="20"/>
       <c r="BI123" s="20"/>
-      <c r="BJ123" s="32"/>
+      <c r="BJ123" s="31"/>
       <c r="BK123" s="20"/>
       <c r="BL123" s="21"/>
       <c r="BM123" s="21"/>
@@ -12987,140 +12980,140 @@
       <c r="BT123" s="21"/>
     </row>
     <row r="125" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A125" s="33" t="s">
+      <c r="A125" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="B125" s="32"/>
+      <c r="C125" s="32"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
+      <c r="F125" s="32"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+      <c r="I125" s="32"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="32"/>
+      <c r="L125" s="32"/>
+      <c r="M125" s="32"/>
+      <c r="N125" s="32"/>
+      <c r="O125" s="32"/>
+      <c r="P125" s="32"/>
+      <c r="Q125" s="32"/>
+      <c r="R125" s="32"/>
+      <c r="S125" s="32"/>
+      <c r="T125" s="32"/>
+      <c r="U125" s="32"/>
+      <c r="V125" s="32"/>
+      <c r="W125" s="32"/>
+      <c r="X125" s="32"/>
+      <c r="Y125" s="32"/>
+      <c r="Z125" s="32"/>
+      <c r="AA125" s="32"/>
+      <c r="AB125" s="32"/>
+      <c r="AC125" s="32"/>
+    </row>
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A126" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="B126" s="32"/>
+      <c r="C126" s="32"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
+      <c r="J126" s="32"/>
+      <c r="K126" s="32"/>
+      <c r="L126" s="32"/>
+      <c r="M126" s="32"/>
+      <c r="N126" s="32"/>
+      <c r="O126" s="32"/>
+      <c r="P126" s="32"/>
+      <c r="Q126" s="32"/>
+      <c r="R126" s="32"/>
+      <c r="S126" s="32"/>
+      <c r="T126" s="32"/>
+      <c r="U126" s="32"/>
+      <c r="V126" s="32"/>
+      <c r="W126" s="32"/>
+      <c r="X126" s="32"/>
+      <c r="Y126" s="32"/>
+      <c r="Z126" s="32"/>
+      <c r="AA126" s="32"/>
+      <c r="AB126" s="32"/>
+      <c r="AC126" s="32"/>
+    </row>
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A127" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="B125" s="33"/>
-      <c r="C125" s="33"/>
-      <c r="D125" s="33"/>
-      <c r="E125" s="33"/>
-      <c r="F125" s="33"/>
-      <c r="G125" s="33"/>
-      <c r="H125" s="33"/>
-      <c r="I125" s="33"/>
-      <c r="J125" s="33"/>
-      <c r="K125" s="33"/>
-      <c r="L125" s="33"/>
-      <c r="M125" s="33"/>
-      <c r="N125" s="33"/>
-      <c r="O125" s="33"/>
-      <c r="P125" s="33"/>
-      <c r="Q125" s="33"/>
-      <c r="R125" s="33"/>
-      <c r="S125" s="33"/>
-      <c r="T125" s="33"/>
-      <c r="U125" s="33"/>
-      <c r="V125" s="33"/>
-      <c r="W125" s="33"/>
-      <c r="X125" s="33"/>
-      <c r="Y125" s="33"/>
-      <c r="Z125" s="33"/>
-      <c r="AA125" s="33"/>
-      <c r="AB125" s="33"/>
-      <c r="AC125" s="33"/>
-    </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A126" s="33" t="s">
+      <c r="B127" s="32"/>
+      <c r="C127" s="32"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="32"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+      <c r="I127" s="32"/>
+      <c r="J127" s="32"/>
+      <c r="K127" s="32"/>
+      <c r="L127" s="32"/>
+      <c r="M127" s="32"/>
+      <c r="N127" s="32"/>
+      <c r="O127" s="32"/>
+      <c r="P127" s="32"/>
+      <c r="Q127" s="32"/>
+      <c r="R127" s="32"/>
+      <c r="S127" s="32"/>
+      <c r="T127" s="32"/>
+      <c r="U127" s="32"/>
+      <c r="V127" s="32"/>
+      <c r="W127" s="32"/>
+      <c r="X127" s="32"/>
+      <c r="Y127" s="32"/>
+      <c r="Z127" s="32"/>
+      <c r="AA127" s="32"/>
+      <c r="AB127" s="32"/>
+      <c r="AC127" s="32"/>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A128" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="B126" s="33"/>
-      <c r="C126" s="33"/>
-      <c r="D126" s="33"/>
-      <c r="E126" s="33"/>
-      <c r="F126" s="33"/>
-      <c r="G126" s="33"/>
-      <c r="H126" s="33"/>
-      <c r="I126" s="33"/>
-      <c r="J126" s="33"/>
-      <c r="K126" s="33"/>
-      <c r="L126" s="33"/>
-      <c r="M126" s="33"/>
-      <c r="N126" s="33"/>
-      <c r="O126" s="33"/>
-      <c r="P126" s="33"/>
-      <c r="Q126" s="33"/>
-      <c r="R126" s="33"/>
-      <c r="S126" s="33"/>
-      <c r="T126" s="33"/>
-      <c r="U126" s="33"/>
-      <c r="V126" s="33"/>
-      <c r="W126" s="33"/>
-      <c r="X126" s="33"/>
-      <c r="Y126" s="33"/>
-      <c r="Z126" s="33"/>
-      <c r="AA126" s="33"/>
-      <c r="AB126" s="33"/>
-      <c r="AC126" s="33"/>
-    </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A127" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="B127" s="33"/>
-      <c r="C127" s="33"/>
-      <c r="D127" s="33"/>
-      <c r="E127" s="33"/>
-      <c r="F127" s="33"/>
-      <c r="G127" s="33"/>
-      <c r="H127" s="33"/>
-      <c r="I127" s="33"/>
-      <c r="J127" s="33"/>
-      <c r="K127" s="33"/>
-      <c r="L127" s="33"/>
-      <c r="M127" s="33"/>
-      <c r="N127" s="33"/>
-      <c r="O127" s="33"/>
-      <c r="P127" s="33"/>
-      <c r="Q127" s="33"/>
-      <c r="R127" s="33"/>
-      <c r="S127" s="33"/>
-      <c r="T127" s="33"/>
-      <c r="U127" s="33"/>
-      <c r="V127" s="33"/>
-      <c r="W127" s="33"/>
-      <c r="X127" s="33"/>
-      <c r="Y127" s="33"/>
-      <c r="Z127" s="33"/>
-      <c r="AA127" s="33"/>
-      <c r="AB127" s="33"/>
-      <c r="AC127" s="33"/>
-    </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A128" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="B128" s="33"/>
-      <c r="C128" s="33"/>
-      <c r="D128" s="33"/>
-      <c r="E128" s="33"/>
-      <c r="F128" s="33"/>
-      <c r="G128" s="33"/>
-      <c r="H128" s="33"/>
-      <c r="I128" s="33"/>
-      <c r="J128" s="33"/>
-      <c r="K128" s="33"/>
-      <c r="L128" s="33"/>
-      <c r="M128" s="33"/>
-      <c r="N128" s="33"/>
-      <c r="O128" s="33"/>
-      <c r="P128" s="33"/>
-      <c r="Q128" s="33"/>
-      <c r="R128" s="33"/>
-      <c r="S128" s="33"/>
-      <c r="T128" s="33"/>
-      <c r="U128" s="33"/>
-      <c r="V128" s="33"/>
-      <c r="W128" s="33"/>
-      <c r="X128" s="33"/>
-      <c r="Y128" s="33"/>
-      <c r="Z128" s="33"/>
-      <c r="AA128" s="33"/>
-      <c r="AB128" s="33"/>
-      <c r="AC128" s="33"/>
+      <c r="B128" s="32"/>
+      <c r="C128" s="32"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="32"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+      <c r="I128" s="32"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="32"/>
+      <c r="L128" s="32"/>
+      <c r="M128" s="32"/>
+      <c r="N128" s="32"/>
+      <c r="O128" s="32"/>
+      <c r="P128" s="32"/>
+      <c r="Q128" s="32"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="32"/>
+      <c r="T128" s="32"/>
+      <c r="U128" s="32"/>
+      <c r="V128" s="32"/>
+      <c r="W128" s="32"/>
+      <c r="X128" s="32"/>
+      <c r="Y128" s="32"/>
+      <c r="Z128" s="32"/>
+      <c r="AA128" s="32"/>
+      <c r="AB128" s="32"/>
+      <c r="AC128" s="32"/>
     </row>
     <row r="130" ht="16" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A130" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -13195,2447 +13188,2447 @@
       <c r="BT130" s="15"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="34" t="s">
+      <c r="A131" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="B131" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="C131" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="B131" s="34" t="s">
+      <c r="D131" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="C131" s="34" t="s">
+      <c r="E131" s="33"/>
+      <c r="F131" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G131" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="D131" s="34" t="s">
+      <c r="H131" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="E131" s="34"/>
-      <c r="F131" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="G131" s="34" t="s">
+      <c r="I131" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="H131" s="34" t="s">
+    </row>
+    <row r="132" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="I131" s="34" t="s">
+      <c r="B132" s="34" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="132" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="35" t="s">
+      <c r="C132" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B132" s="35" t="s">
+      <c r="D132" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="C132" s="25" t="s">
+      <c r="E132" s="25"/>
+      <c r="F132" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G132" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="D132" s="25" t="s">
+      <c r="H132" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="E132" s="25"/>
-      <c r="F132" s="36" t="s">
+      <c r="I132" s="25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="133" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C133" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D133" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="E133" s="25"/>
+      <c r="F133" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G132" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="H132" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I132" s="25" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="133" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="35" t="s">
+      <c r="G133" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="B133" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C133" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D133" s="25" t="s">
+      <c r="H133" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I133" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="E133" s="25"/>
-      <c r="F133" s="36" t="s">
+    </row>
+    <row r="134" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B134" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C134" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D134" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="E134" s="25"/>
+      <c r="F134" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G133" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="H133" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I133" s="25" t="s">
+      <c r="G134" s="35" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="134" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B134" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C134" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D134" s="25" t="s">
+      <c r="H134" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I134" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="E134" s="25"/>
-      <c r="F134" s="36" t="s">
+    </row>
+    <row r="135" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C135" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D135" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="E135" s="25"/>
+      <c r="F135" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G134" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="H134" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I134" s="25" t="s">
+      <c r="G135" s="35" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="135" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B135" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C135" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D135" s="25" t="s">
+      <c r="H135" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I135" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="36" t="s">
+    </row>
+    <row r="136" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C136" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D136" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="E136" s="25"/>
+      <c r="F136" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G135" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="H135" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I135" s="25" t="s">
+      <c r="G136" s="35" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="136" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B136" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C136" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D136" s="25" t="s">
+      <c r="H136" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I136" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E136" s="25"/>
-      <c r="F136" s="36" t="s">
+    </row>
+    <row r="137" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B137" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D137" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E137" s="25"/>
+      <c r="F137" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G136" s="36" t="s">
+      <c r="G137" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I137" s="25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="138" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C138" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="H136" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I136" s="25" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="137" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B137" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D137" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="E137" s="25"/>
-      <c r="F137" s="36" t="s">
+      <c r="D138" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E138" s="25"/>
+      <c r="F138" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G137" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="H137" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I137" s="25" t="s">
+      <c r="G138" s="35" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="138" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B138" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D138" s="25" t="s">
+      <c r="H138" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I138" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="E138" s="25"/>
-      <c r="F138" s="36" t="s">
+    </row>
+    <row r="139" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B139" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D139" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="E139" s="25"/>
+      <c r="F139" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G138" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="H138" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I138" s="25" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="139" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B139" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C139" s="25" t="s">
+      <c r="G139" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="D139" s="25" t="s">
+      <c r="H139" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I139" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="E139" s="25"/>
-      <c r="F139" s="36" t="s">
+    </row>
+    <row r="140" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B140" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D140" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="E140" s="25"/>
+      <c r="F140" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G139" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="H139" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I139" s="25" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="140" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B140" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C140" s="25" t="s">
+      <c r="G140" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="D140" s="25" t="s">
+      <c r="H140" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I140" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="E140" s="25"/>
-      <c r="F140" s="36" t="s">
+    </row>
+    <row r="141" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B141" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D141" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E141" s="25"/>
+      <c r="F141" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G140" s="36" t="s">
-        <v>298</v>
-      </c>
-      <c r="H140" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I140" s="25" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="141" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C141" s="25" t="s">
+      <c r="G141" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="D141" s="25" t="s">
+      <c r="H141" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I141" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="E141" s="25"/>
-      <c r="F141" s="36" t="s">
+    </row>
+    <row r="142" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B142" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C142" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="D142" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="E142" s="25"/>
+      <c r="F142" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G141" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="H141" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I141" s="25" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="142" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B142" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C142" s="25" t="s">
+      <c r="G142" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="D142" s="25" t="s">
+      <c r="H142" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I142" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="E142" s="25"/>
-      <c r="F142" s="36" t="s">
+    </row>
+    <row r="143" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B143" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D143" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="E143" s="25"/>
+      <c r="F143" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="G142" s="36" t="s">
-        <v>306</v>
-      </c>
-      <c r="H142" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I142" s="25" t="s">
+      <c r="G143" s="35" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="143" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B143" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C143" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D143" s="25" t="s">
+      <c r="H143" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I143" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="G143" s="36" t="s">
+    </row>
+    <row r="144" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B144" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="H143" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I143" s="25" t="s">
+      <c r="C144" s="25" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="144" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B144" s="35" t="s">
+      <c r="D144" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="C144" s="25" t="s">
+      <c r="E144" s="25"/>
+      <c r="F144" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G144" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="D144" s="25" t="s">
+      <c r="H144" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I144" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="E144" s="25"/>
-      <c r="F144" s="36" t="s">
+    </row>
+    <row r="145" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C145" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="D145" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="E145" s="25"/>
+      <c r="F145" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G144" s="36" t="s">
+      <c r="G145" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="H145" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I145" s="25" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="146" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C146" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="D146" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="E146" s="25"/>
+      <c r="F146" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G146" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="H146" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I146" s="25" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="147" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C147" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="H144" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I144" s="25" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="145" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B145" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C145" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="D145" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="E145" s="25"/>
-      <c r="F145" s="36" t="s">
+      <c r="D147" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="E147" s="25"/>
+      <c r="F147" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G145" s="36" t="s">
-        <v>318</v>
-      </c>
-      <c r="H145" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I145" s="25" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="146" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C146" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="D146" s="25" t="s">
-        <v>321</v>
-      </c>
-      <c r="E146" s="25"/>
-      <c r="F146" s="36" t="s">
+      <c r="G147" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="H147" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I147" s="25" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="148" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C148" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="D148" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="E148" s="25"/>
+      <c r="F148" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G146" s="36" t="s">
-        <v>322</v>
-      </c>
-      <c r="H146" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I146" s="25" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="147" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B147" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C147" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="D147" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="E147" s="25"/>
-      <c r="F147" s="36" t="s">
+      <c r="G148" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="H148" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I148" s="25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="149" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B149" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D149" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="E149" s="25"/>
+      <c r="F149" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G147" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="H147" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I147" s="25" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="148" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B148" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C148" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="D148" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="E148" s="25"/>
-      <c r="F148" s="36" t="s">
+      <c r="G149" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H149" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I149" s="25" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="150" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B150" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C150" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="D150" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E150" s="25"/>
+      <c r="F150" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G148" s="36" t="s">
+      <c r="G150" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I150" s="25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B151" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C151" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="H148" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I148" s="25" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="149" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B149" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C149" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D149" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="E149" s="25"/>
-      <c r="F149" s="36" t="s">
+      <c r="D151" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="E151" s="25"/>
+      <c r="F151" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G149" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="H149" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I149" s="25" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="150" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B150" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C150" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="D150" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="E150" s="25"/>
-      <c r="F150" s="36" t="s">
+      <c r="G151" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="H151" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I151" s="25" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="152" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B152" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C152" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D152" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="E152" s="25"/>
+      <c r="F152" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G150" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="H150" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I150" s="25" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="151" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B151" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D151" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="E151" s="25"/>
-      <c r="F151" s="36" t="s">
+      <c r="G152" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="H152" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I152" s="25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="E153" s="25"/>
+      <c r="F153" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G151" s="36" t="s">
-        <v>338</v>
-      </c>
-      <c r="H151" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I151" s="25" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="152" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D152" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="E152" s="25"/>
-      <c r="F152" s="36" t="s">
+      <c r="G153" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="H153" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I153" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="154" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B154" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C154" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="D154" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="E154" s="25"/>
+      <c r="F154" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G152" s="36" t="s">
-        <v>341</v>
-      </c>
-      <c r="H152" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I152" s="25" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="153" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D153" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="E153" s="25"/>
-      <c r="F153" s="36" t="s">
+      <c r="G154" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="H154" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I154" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="155" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B155" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C155" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D155" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="E155" s="25"/>
+      <c r="F155" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G153" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="H153" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I153" s="25" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="154" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>346</v>
-      </c>
-      <c r="D154" s="25" t="s">
-        <v>347</v>
-      </c>
-      <c r="E154" s="25"/>
-      <c r="F154" s="36" t="s">
+      <c r="G155" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="H155" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I155" s="25" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="156" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B156" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C156" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D156" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="E156" s="25"/>
+      <c r="F156" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G156" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H156" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I156" s="25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="157" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B157" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C157" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D157" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="E157" s="25"/>
+      <c r="F157" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G157" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="H157" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I157" s="25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="158" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B158" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C158" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D158" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="E158" s="25"/>
+      <c r="F158" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G158" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="H158" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I158" s="25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="159" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D159" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="E159" s="25"/>
+      <c r="F159" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G159" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="H159" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I159" s="25" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="160" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B160" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D160" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="E160" s="25"/>
+      <c r="F160" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G160" s="35" t="s">
+        <v>366</v>
+      </c>
+      <c r="H160" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I160" s="25" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="161" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B161" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C161" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D161" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="E161" s="25"/>
+      <c r="F161" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G161" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="H161" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I161" s="25" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="162" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B162" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C162" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D162" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="E162" s="25"/>
+      <c r="F162" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G162" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="H162" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I162" s="25" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="163" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B163" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C163" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D163" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="E163" s="25"/>
+      <c r="F163" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G163" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="H163" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I163" s="25" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="164" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B164" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C164" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D164" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="E164" s="25"/>
+      <c r="F164" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G164" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="H164" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I164" s="25" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="165" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B165" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C165" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D165" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="E165" s="25"/>
+      <c r="F165" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G154" s="36" t="s">
-        <v>348</v>
-      </c>
-      <c r="H154" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I154" s="25" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="155" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B155" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C155" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D155" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="E155" s="25"/>
-      <c r="F155" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G155" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="H155" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I155" s="25" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="156" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B156" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C156" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D156" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="E156" s="25"/>
-      <c r="F156" s="36" t="s">
+      <c r="G165" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="H165" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I165" s="25" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="166" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B166" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C166" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D166" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="E166" s="25"/>
+      <c r="F166" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G166" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="H166" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I166" s="25" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="167" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B167" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C167" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="D167" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="E167" s="25"/>
+      <c r="F167" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G167" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="H167" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I167" s="25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="168" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B168" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C168" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="D168" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="E168" s="25"/>
+      <c r="F168" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G168" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="H168" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I168" s="25" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="169" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B169" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C169" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D169" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="E169" s="25"/>
+      <c r="F169" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G156" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="H156" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I156" s="25" t="s">
+      <c r="G169" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="H169" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I169" s="25" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="170" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B170" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C170" s="25" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="157" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B157" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="C157" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D157" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="36" t="s">
+      <c r="D170" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="E170" s="25"/>
+      <c r="F170" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="G157" s="36" t="s">
-        <v>359</v>
-      </c>
-      <c r="H157" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I157" s="25" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="158" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B158" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C158" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D158" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="E158" s="25"/>
-      <c r="F158" s="36" t="s">
+      <c r="G170" s="35" t="s">
+        <v>398</v>
+      </c>
+      <c r="H170" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I170" s="25" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="171" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B171" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C171" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="E171" s="25"/>
+      <c r="F171" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="G158" s="36" t="s">
-        <v>362</v>
-      </c>
-      <c r="H158" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I158" s="25" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="159" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B159" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C159" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D159" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="E159" s="25"/>
-      <c r="F159" s="36" t="s">
+      <c r="G171" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="H171" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I171" s="25" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="172" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B172" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C172" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="D172" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E172" s="25"/>
+      <c r="F172" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="G159" s="36" t="s">
-        <v>365</v>
-      </c>
-      <c r="H159" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I159" s="25" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="160" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B160" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D160" s="25" t="s">
-        <v>367</v>
-      </c>
-      <c r="E160" s="25"/>
-      <c r="F160" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G160" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="H160" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I160" s="25" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="161" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B161" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C161" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D161" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="E161" s="25"/>
-      <c r="F161" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G161" s="36" t="s">
-        <v>371</v>
-      </c>
-      <c r="H161" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I161" s="25" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="162" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B162" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C162" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D162" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E162" s="25"/>
-      <c r="F162" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G162" s="36" t="s">
-        <v>374</v>
-      </c>
-      <c r="H162" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I162" s="25" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="163" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B163" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C163" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D163" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="E163" s="25"/>
-      <c r="F163" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G163" s="36" t="s">
-        <v>377</v>
-      </c>
-      <c r="H163" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I163" s="25" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="164" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B164" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C164" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D164" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="36" t="s">
+      <c r="G172" s="35" t="s">
+        <v>405</v>
+      </c>
+      <c r="H172" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I172" s="25" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="173" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B173" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="C173" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="E173" s="25"/>
+      <c r="F173" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G164" s="36" t="s">
-        <v>380</v>
-      </c>
-      <c r="H164" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I164" s="25" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="165" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B165" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C165" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D165" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="E165" s="25"/>
-      <c r="F165" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G165" s="36" t="s">
-        <v>383</v>
-      </c>
-      <c r="H165" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I165" s="25" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="166" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B166" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C166" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D166" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="E166" s="25"/>
-      <c r="F166" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G166" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="H166" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I166" s="25" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="167" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B167" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C167" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="D167" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="E167" s="25"/>
-      <c r="F167" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G167" s="36" t="s">
-        <v>390</v>
-      </c>
-      <c r="H167" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I167" s="25" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="168" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B168" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C168" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="D168" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="E168" s="25"/>
-      <c r="F168" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G168" s="36" t="s">
-        <v>394</v>
-      </c>
-      <c r="H168" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I168" s="25" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="169" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B169" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C169" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D169" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="E169" s="25"/>
-      <c r="F169" s="36" t="s">
+      <c r="G173" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="H173" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I173" s="25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="174" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B174" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C174" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D174" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="E174" s="25"/>
+      <c r="F174" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G169" s="36" t="s">
-        <v>397</v>
-      </c>
-      <c r="H169" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I169" s="25" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="170" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B170" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C170" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D170" s="25" t="s">
-        <v>399</v>
-      </c>
-      <c r="E170" s="25"/>
-      <c r="F170" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G170" s="36" t="s">
-        <v>400</v>
-      </c>
-      <c r="H170" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I170" s="25" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="171" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B171" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C171" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D171" s="25" t="s">
-        <v>402</v>
-      </c>
-      <c r="E171" s="25"/>
-      <c r="F171" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G171" s="36" t="s">
-        <v>403</v>
-      </c>
-      <c r="H171" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I171" s="25" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="172" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B172" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C172" s="25" t="s">
-        <v>405</v>
-      </c>
-      <c r="D172" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G172" s="36" t="s">
-        <v>407</v>
-      </c>
-      <c r="H172" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I172" s="25" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="173" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B173" s="35" t="s">
-        <v>409</v>
-      </c>
-      <c r="C173" s="25" t="s">
-        <v>410</v>
-      </c>
-      <c r="D173" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="E173" s="25"/>
-      <c r="F173" s="36" t="s">
+      <c r="G174" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="H174" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I174" s="25" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="175" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B175" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C175" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D175" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="E175" s="25"/>
+      <c r="F175" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G173" s="36" t="s">
-        <v>412</v>
-      </c>
-      <c r="H173" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I173" s="25" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="174" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B174" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C174" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D174" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="E174" s="25"/>
-      <c r="F174" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G174" s="36" t="s">
-        <v>415</v>
-      </c>
-      <c r="H174" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I174" s="25" t="s">
+      <c r="G175" s="35" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="175" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B175" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C175" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D175" s="25" t="s">
+      <c r="H175" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I175" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="E175" s="25"/>
-      <c r="F175" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G175" s="36" t="s">
-        <v>418</v>
-      </c>
-      <c r="H175" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I175" s="25" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="176" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B176" s="35" t="s">
-        <v>272</v>
+      <c r="A176" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B176" s="34" t="s">
+        <v>270</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D176" s="25" t="s">
         <v>156</v>
       </c>
       <c r="E176" s="25"/>
-      <c r="F176" s="36" t="s">
+      <c r="F176" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G176" s="36" t="s">
+      <c r="G176" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="H176" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I176" s="25" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="177" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B177" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C177" s="25" t="s">
         <v>420</v>
       </c>
-      <c r="H176" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I176" s="25" t="s">
+      <c r="D177" s="25" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="177" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B177" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C177" s="25" t="s">
+      <c r="E177" s="25"/>
+      <c r="F177" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G177" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="D177" s="25" t="s">
+      <c r="H177" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I177" s="25" t="s">
         <v>423</v>
       </c>
-      <c r="E177" s="25"/>
-      <c r="F177" s="36" t="s">
+    </row>
+    <row r="178" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B178" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C178" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D178" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="E178" s="25"/>
+      <c r="F178" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G177" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="H177" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I177" s="25" t="s">
+      <c r="G178" s="35" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="178" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B178" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C178" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D178" s="25" t="s">
+      <c r="H178" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I178" s="25" t="s">
         <v>426</v>
       </c>
-      <c r="E178" s="25"/>
-      <c r="F178" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G178" s="36" t="s">
-        <v>427</v>
-      </c>
-      <c r="H178" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I178" s="25" t="s">
-        <v>428</v>
-      </c>
     </row>
     <row r="179" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B179" s="35" t="s">
-        <v>272</v>
+      <c r="A179" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B179" s="34" t="s">
+        <v>270</v>
       </c>
       <c r="C179" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D179" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="E179" s="25"/>
+      <c r="F179" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G179" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="H179" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I179" s="25" t="s">
         <v>429</v>
       </c>
-      <c r="E179" s="25"/>
-      <c r="F179" s="36" t="s">
+    </row>
+    <row r="180" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B180" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C180" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="D180" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="E180" s="25"/>
+      <c r="F180" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G179" s="36" t="s">
-        <v>430</v>
-      </c>
-      <c r="H179" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I179" s="25" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="180" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B180" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C180" s="25" t="s">
+      <c r="G180" s="35" t="s">
         <v>432</v>
       </c>
-      <c r="D180" s="25" t="s">
+      <c r="H180" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I180" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="E180" s="25"/>
-      <c r="F180" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G180" s="36" t="s">
+    </row>
+    <row r="181" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B181" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="C181" s="25" t="s">
         <v>434</v>
       </c>
-      <c r="H180" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I180" s="25" t="s">
+      <c r="D181" s="25" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="181" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B181" s="35" t="s">
-        <v>382</v>
-      </c>
-      <c r="C181" s="25" t="s">
+      <c r="E181" s="25"/>
+      <c r="F181" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G181" s="35" t="s">
         <v>436</v>
       </c>
-      <c r="D181" s="25" t="s">
+      <c r="H181" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I181" s="25" t="s">
         <v>437</v>
       </c>
-      <c r="E181" s="25"/>
-      <c r="F181" s="36" t="s">
+    </row>
+    <row r="182" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B182" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C182" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="D182" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="E182" s="25"/>
+      <c r="F182" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G181" s="36" t="s">
-        <v>438</v>
-      </c>
-      <c r="H181" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I181" s="25" t="s">
+      <c r="G182" s="35" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="182" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B182" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C182" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="D182" s="25" t="s">
+      <c r="H182" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I182" s="25" t="s">
         <v>440</v>
       </c>
-      <c r="E182" s="25"/>
-      <c r="F182" s="36" t="s">
+    </row>
+    <row r="183" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B183" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C183" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="D183" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="E183" s="25"/>
+      <c r="F183" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G182" s="36" t="s">
-        <v>441</v>
-      </c>
-      <c r="H182" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I182" s="25" t="s">
+      <c r="G183" s="35" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="183" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B183" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C183" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="D183" s="25" t="s">
+      <c r="H183" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I183" s="25" t="s">
         <v>443</v>
       </c>
-      <c r="E183" s="25"/>
-      <c r="F183" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G183" s="36" t="s">
-        <v>444</v>
-      </c>
-      <c r="H183" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I183" s="25" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="184" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B184" s="35" t="s">
-        <v>272</v>
+      <c r="A184" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B184" s="34" t="s">
+        <v>270</v>
       </c>
       <c r="C184" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D184" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="E184" s="25"/>
+      <c r="F184" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G184" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="H184" s="37" t="s">
         <v>446</v>
       </c>
-      <c r="E184" s="25"/>
-      <c r="F184" s="36" t="s">
+      <c r="I184" s="25" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="185" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B185" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="C185" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="D185" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="E185" s="25"/>
+      <c r="F185" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G185" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="H185" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I185" s="25" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="186" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B186" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C186" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="D186" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="E186" s="25"/>
+      <c r="F186" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G186" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="H186" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I186" s="25" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="187" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B187" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C187" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D187" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E187" s="25"/>
+      <c r="F187" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G187" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="H187" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I187" s="25" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="188" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B188" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C188" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D188" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="E188" s="25"/>
+      <c r="F188" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G188" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="H188" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I188" s="25" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="189" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B189" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C189" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="D189" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="E189" s="25"/>
+      <c r="F189" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="H189" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I189" s="25" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="190" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B190" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C190" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="D190" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="E190" s="25"/>
+      <c r="F190" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="H190" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I190" s="25" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="191" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B191" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C191" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D191" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="E191" s="25"/>
+      <c r="F191" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="H191" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I191" s="25" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="192" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B192" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C192" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="D192" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="E192" s="25"/>
+      <c r="F192" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="H192" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I192" s="25" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="193" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B193" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C193" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="D193" s="25" t="s">
+        <v>481</v>
+      </c>
+      <c r="E193" s="25"/>
+      <c r="F193" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" s="35" t="s">
+        <v>482</v>
+      </c>
+      <c r="H193" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I193" s="25" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="194" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B194" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C194" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="D194" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E194" s="25"/>
+      <c r="F194" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="H194" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I194" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="195" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B195" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C195" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="D195" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="E195" s="25"/>
+      <c r="F195" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="G195" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="H195" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I195" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="196" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B196" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="C196" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D196" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="E196" s="25"/>
+      <c r="F196" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G196" s="35" t="s">
+        <v>496</v>
+      </c>
+      <c r="H196" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I196" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="197" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B197" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C197" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="D197" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="E197" s="25"/>
+      <c r="F197" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G197" s="35" t="s">
+        <v>499</v>
+      </c>
+      <c r="H197" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I197" s="25" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="198" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B198" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C198" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D198" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E198" s="25"/>
+      <c r="F198" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G198" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="H198" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I198" s="25" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="199" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B199" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C199" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D199" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="E199" s="25"/>
+      <c r="F199" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G199" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="H199" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I199" s="25" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="200" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B200" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C200" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="D200" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="E200" s="25"/>
+      <c r="F200" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G200" s="35" t="s">
+        <v>509</v>
+      </c>
+      <c r="H200" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I200" s="25" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="201" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B201" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C201" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="D201" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="E201" s="25"/>
+      <c r="F201" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G201" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="H201" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I201" s="25" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="202" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B202" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C202" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="D202" s="25" t="s">
+        <v>515</v>
+      </c>
+      <c r="E202" s="25"/>
+      <c r="F202" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G202" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="H202" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I202" s="25" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="203" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B203" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C203" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="E203" s="25"/>
+      <c r="F203" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G184" s="36" t="s">
-        <v>447</v>
-      </c>
-      <c r="H184" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="I184" s="25" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="185" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B185" s="35" t="s">
-        <v>450</v>
-      </c>
-      <c r="C185" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="D185" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G185" s="36" t="s">
-        <v>454</v>
-      </c>
-      <c r="H185" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I185" s="25" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="186" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B186" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C186" s="25" t="s">
-        <v>456</v>
-      </c>
-      <c r="D186" s="25" t="s">
-        <v>457</v>
-      </c>
-      <c r="E186" s="25"/>
-      <c r="F186" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G186" s="36" t="s">
-        <v>458</v>
-      </c>
-      <c r="H186" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I186" s="25" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="187" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B187" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C187" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="D187" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G187" s="36" t="s">
-        <v>462</v>
-      </c>
-      <c r="H187" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I187" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="188" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B188" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="D188" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="E188" s="25"/>
-      <c r="F188" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G188" s="36" t="s">
-        <v>465</v>
-      </c>
-      <c r="H188" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I188" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="189" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B189" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C189" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="D189" s="25" t="s">
-        <v>468</v>
-      </c>
-      <c r="E189" s="25"/>
-      <c r="F189" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G189" s="36" t="s">
-        <v>469</v>
-      </c>
-      <c r="H189" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I189" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="190" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B190" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C190" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="D190" s="25" t="s">
-        <v>472</v>
-      </c>
-      <c r="E190" s="25"/>
-      <c r="F190" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G190" s="36" t="s">
-        <v>473</v>
-      </c>
-      <c r="H190" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I190" s="25" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="191" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B191" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C191" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D191" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="E191" s="25"/>
-      <c r="F191" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G191" s="36" t="s">
-        <v>476</v>
-      </c>
-      <c r="H191" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I191" s="25" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="192" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B192" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C192" s="25" t="s">
-        <v>478</v>
-      </c>
-      <c r="D192" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="E192" s="25"/>
-      <c r="F192" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G192" s="36" t="s">
-        <v>480</v>
-      </c>
-      <c r="H192" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I192" s="25" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="193" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B193" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C193" s="25" t="s">
-        <v>482</v>
-      </c>
-      <c r="D193" s="25" t="s">
-        <v>483</v>
-      </c>
-      <c r="E193" s="25"/>
-      <c r="F193" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G193" s="36" t="s">
-        <v>484</v>
-      </c>
-      <c r="H193" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I193" s="25" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="194" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B194" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C194" s="25" t="s">
-        <v>486</v>
-      </c>
-      <c r="D194" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="E194" s="25"/>
-      <c r="F194" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G194" s="36" t="s">
-        <v>488</v>
-      </c>
-      <c r="H194" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I194" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="195" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B195" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C195" s="25" t="s">
-        <v>490</v>
-      </c>
-      <c r="D195" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="E195" s="25"/>
-      <c r="F195" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="G195" s="36" t="s">
-        <v>492</v>
-      </c>
-      <c r="H195" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I195" s="25" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="196" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B196" s="35" t="s">
-        <v>494</v>
-      </c>
-      <c r="C196" s="25" t="s">
+      <c r="G203" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="H203" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I203" s="25" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="204" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B204" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C204" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="E204" s="25"/>
+      <c r="F204" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="D196" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="E196" s="25"/>
-      <c r="F196" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G196" s="36" t="s">
-        <v>498</v>
-      </c>
-      <c r="H196" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I196" s="25" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="197" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B197" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="D197" s="25" t="s">
-        <v>500</v>
-      </c>
-      <c r="E197" s="25"/>
-      <c r="F197" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G197" s="36" t="s">
-        <v>501</v>
-      </c>
-      <c r="H197" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I197" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="198" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B198" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C198" s="25" t="s">
+      <c r="G204" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="H204" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I204" s="25" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="205" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B205" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C205" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="D205" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="E205" s="25"/>
+      <c r="F205" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="D198" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="E198" s="25"/>
-      <c r="F198" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G198" s="36" t="s">
-        <v>504</v>
-      </c>
-      <c r="H198" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I198" s="25" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="199" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B199" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C199" s="25" t="s">
+      <c r="G205" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="H205" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I205" s="25" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="206" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B206" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C206" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="D206" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="E206" s="25"/>
+      <c r="F206" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="D199" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="E199" s="25"/>
-      <c r="F199" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G199" s="36" t="s">
-        <v>507</v>
-      </c>
-      <c r="H199" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I199" s="25" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="200" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B200" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C200" s="25" t="s">
-        <v>509</v>
-      </c>
-      <c r="D200" s="25" t="s">
-        <v>510</v>
-      </c>
-      <c r="E200" s="25"/>
-      <c r="F200" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G200" s="36" t="s">
-        <v>511</v>
-      </c>
-      <c r="H200" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I200" s="25" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="201" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B201" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C201" s="25" t="s">
-        <v>513</v>
-      </c>
-      <c r="D201" s="25" t="s">
-        <v>514</v>
-      </c>
-      <c r="E201" s="25"/>
-      <c r="F201" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G201" s="36" t="s">
-        <v>515</v>
-      </c>
-      <c r="H201" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I201" s="25" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="202" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B202" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>509</v>
-      </c>
-      <c r="D202" s="25" t="s">
-        <v>517</v>
-      </c>
-      <c r="E202" s="25"/>
-      <c r="F202" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G202" s="36" t="s">
-        <v>518</v>
-      </c>
-      <c r="H202" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I202" s="25" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="203" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B203" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C203" s="25" t="s">
+      <c r="G206" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="H206" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I206" s="25" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="207" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B207" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C207" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="D207" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="E207" s="25"/>
+      <c r="F207" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="D203" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="E203" s="25"/>
-      <c r="F203" s="36" t="s">
+      <c r="G207" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="H207" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I207" s="25" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="208" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B208" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="C208" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="D208" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="E208" s="25"/>
+      <c r="F208" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G203" s="36" t="s">
-        <v>521</v>
-      </c>
-      <c r="H203" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I203" s="25" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="204" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B204" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C204" s="25" t="s">
-        <v>523</v>
-      </c>
-      <c r="D204" s="25" t="s">
-        <v>524</v>
-      </c>
-      <c r="E204" s="25"/>
-      <c r="F204" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G204" s="36" t="s">
-        <v>525</v>
-      </c>
-      <c r="H204" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I204" s="25" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="205" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B205" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C205" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="D205" s="25" t="s">
-        <v>528</v>
-      </c>
-      <c r="E205" s="25"/>
-      <c r="F205" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G205" s="36" t="s">
-        <v>529</v>
-      </c>
-      <c r="H205" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I205" s="25" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="206" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B206" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C206" s="25" t="s">
-        <v>531</v>
-      </c>
-      <c r="D206" s="25" t="s">
-        <v>532</v>
-      </c>
-      <c r="E206" s="25"/>
-      <c r="F206" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G206" s="36" t="s">
-        <v>533</v>
-      </c>
-      <c r="H206" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I206" s="25" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="207" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B207" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C207" s="25" t="s">
-        <v>535</v>
-      </c>
-      <c r="D207" s="25" t="s">
-        <v>536</v>
-      </c>
-      <c r="E207" s="25"/>
-      <c r="F207" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="G207" s="36" t="s">
-        <v>537</v>
-      </c>
-      <c r="H207" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I207" s="25" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="208" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B208" s="35" t="s">
-        <v>539</v>
-      </c>
-      <c r="C208" s="25" t="s">
+      <c r="G208" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="D208" s="25" t="s">
+      <c r="H208" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I208" s="25" t="s">
         <v>541</v>
       </c>
-      <c r="E208" s="25"/>
-      <c r="F208" s="36" t="s">
+    </row>
+    <row r="209" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B209" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C209" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D209" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="E209" s="25"/>
+      <c r="F209" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G208" s="36" t="s">
-        <v>542</v>
-      </c>
-      <c r="H208" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I208" s="25" t="s">
+      <c r="G209" s="35" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="209" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B209" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C209" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="D209" s="25" t="s">
+      <c r="H209" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I209" s="25" t="s">
         <v>544</v>
       </c>
-      <c r="E209" s="25"/>
-      <c r="F209" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G209" s="36" t="s">
-        <v>545</v>
-      </c>
-      <c r="H209" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I209" s="25" t="s">
-        <v>546</v>
-      </c>
     </row>
     <row r="210" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B210" s="35" t="s">
-        <v>272</v>
+      <c r="A210" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B210" s="34" t="s">
+        <v>270</v>
       </c>
       <c r="C210" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D210" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="E210" s="25"/>
+      <c r="F210" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G210" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="H210" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="I210" s="25" t="s">
         <v>547</v>
       </c>
-      <c r="E210" s="25"/>
-      <c r="F210" s="36" t="s">
+    </row>
+    <row r="211" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B211" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="C211" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="D211" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="E211" s="25"/>
+      <c r="F211" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G210" s="36" t="s">
-        <v>548</v>
-      </c>
-      <c r="H210" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="I210" s="25" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="211" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B211" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="C211" s="25" t="s">
+      <c r="G211" s="35" t="s">
         <v>551</v>
       </c>
-      <c r="D211" s="25" t="s">
+      <c r="H211" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I211" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="E211" s="25"/>
-      <c r="F211" s="36" t="s">
+    </row>
+    <row r="212" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B212" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C212" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="D212" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="E212" s="25"/>
+      <c r="F212" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G211" s="36" t="s">
-        <v>553</v>
-      </c>
-      <c r="H211" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I211" s="25" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="212" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B212" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C212" s="25" t="s">
+      <c r="G212" s="35" t="s">
         <v>555</v>
       </c>
-      <c r="D212" s="25" t="s">
+      <c r="H212" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I212" s="25" t="s">
         <v>556</v>
       </c>
-      <c r="E212" s="25"/>
-      <c r="F212" s="36" t="s">
+    </row>
+    <row r="213" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B213" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C213" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="D213" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="E213" s="25"/>
+      <c r="F213" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G212" s="36" t="s">
-        <v>557</v>
-      </c>
-      <c r="H212" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I212" s="25" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="213" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B213" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C213" s="25" t="s">
+      <c r="G213" s="35" t="s">
         <v>559</v>
       </c>
-      <c r="D213" s="25" t="s">
+      <c r="H213" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I213" s="25" t="s">
         <v>560</v>
       </c>
-      <c r="E213" s="25"/>
-      <c r="F213" s="36" t="s">
+    </row>
+    <row r="214" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="B214" s="34" t="s">
+        <v>562</v>
+      </c>
+      <c r="C214" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="D214" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="E214" s="25"/>
+      <c r="F214" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G213" s="36" t="s">
-        <v>561</v>
-      </c>
-      <c r="H213" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I213" s="25" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="214" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="35" t="s">
+      <c r="G214" s="35" t="s">
+        <v>565</v>
+      </c>
+      <c r="H214" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I214" s="25" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="215" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B215" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C215" s="25" t="s">
         <v>563</v>
       </c>
-      <c r="B214" s="35" t="s">
-        <v>564</v>
-      </c>
-      <c r="C214" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="D214" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="E214" s="25"/>
-      <c r="F214" s="36" t="s">
+      <c r="D215" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="E215" s="25"/>
+      <c r="F215" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G214" s="36" t="s">
-        <v>567</v>
-      </c>
-      <c r="H214" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I214" s="25" t="s">
+      <c r="G215" s="35" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="215" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B215" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C215" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="D215" s="25" t="s">
+      <c r="H215" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I215" s="25" t="s">
         <v>569</v>
       </c>
-      <c r="E215" s="25"/>
-      <c r="F215" s="36" t="s">
+    </row>
+    <row r="216" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B216" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C216" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="D216" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="E216" s="25"/>
+      <c r="F216" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G215" s="36" t="s">
-        <v>570</v>
-      </c>
-      <c r="H215" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I215" s="25" t="s">
+      <c r="G216" s="35" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="216" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B216" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C216" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="D216" s="25" t="s">
+      <c r="H216" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I216" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="E216" s="25"/>
-      <c r="F216" s="36" t="s">
+    </row>
+    <row r="217" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B217" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C217" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="D217" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="E217" s="25"/>
+      <c r="F217" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G216" s="36" t="s">
-        <v>573</v>
-      </c>
-      <c r="H216" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I216" s="25" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="217" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B217" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C217" s="25" t="s">
+      <c r="G217" s="35" t="s">
         <v>575</v>
       </c>
-      <c r="D217" s="25" t="s">
+      <c r="H217" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I217" s="25" t="s">
         <v>576</v>
       </c>
-      <c r="E217" s="25"/>
-      <c r="F217" s="36" t="s">
+    </row>
+    <row r="218" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B218" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C218" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="D218" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="E218" s="25"/>
+      <c r="F218" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G217" s="36" t="s">
-        <v>577</v>
-      </c>
-      <c r="H217" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I217" s="25" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="218" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B218" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C218" s="25" t="s">
+      <c r="G218" s="35" t="s">
         <v>579</v>
       </c>
-      <c r="D218" s="25" t="s">
+      <c r="H218" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I218" s="25" t="s">
         <v>580</v>
       </c>
-      <c r="E218" s="25"/>
-      <c r="F218" s="36" t="s">
+    </row>
+    <row r="219" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B219" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C219" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="D219" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="E219" s="25"/>
+      <c r="F219" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G218" s="36" t="s">
-        <v>581</v>
-      </c>
-      <c r="H218" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I218" s="25" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="219" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B219" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C219" s="25" t="s">
+      <c r="G219" s="35" t="s">
         <v>583</v>
       </c>
-      <c r="D219" s="25" t="s">
+      <c r="H219" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I219" s="25" t="s">
         <v>584</v>
       </c>
-      <c r="E219" s="25"/>
-      <c r="F219" s="36" t="s">
+    </row>
+    <row r="220" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B220" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="C220" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="D220" s="25" t="s">
+        <v>585</v>
+      </c>
+      <c r="E220" s="25"/>
+      <c r="F220" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="G219" s="36" t="s">
-        <v>585</v>
-      </c>
-      <c r="H219" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I219" s="25" t="s">
+      <c r="G220" s="35" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="220" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B220" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C220" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="D220" s="25" t="s">
+      <c r="H220" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="I220" s="25" t="s">
         <v>587</v>
       </c>
-      <c r="E220" s="25"/>
-      <c r="F220" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G220" s="36" t="s">
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="H220" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I220" s="25" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="39" t="s">
-        <v>590</v>
-      </c>
-      <c r="B221" s="39"/>
-      <c r="C221" s="39"/>
-      <c r="D221" s="39"/>
-      <c r="E221" s="39"/>
-      <c r="F221" s="39"/>
-      <c r="G221" s="39"/>
-      <c r="H221" s="39"/>
-      <c r="I221" s="39"/>
+      <c r="B221" s="38"/>
+      <c r="C221" s="38"/>
+      <c r="D221" s="38"/>
+      <c r="E221" s="38"/>
+      <c r="F221" s="38"/>
+      <c r="G221" s="38"/>
+      <c r="H221" s="38"/>
+      <c r="I221" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="237">

--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="588">
   <si>
     <t>Project</t>
   </si>
@@ -625,7 +625,7 @@
     <t>시연 시나리오·계정 준비  [TNSM-75]</t>
   </si>
   <si>
-    <t>5.0 최종 마무리 (P4)   [TNSM-5]  09-28 ~ 10-16  ·  진행 중</t>
+    <t>5.0 최종 마무리 (P4)   [TNSM-5]  09-28 ~ 10-16  ·  완료</t>
   </si>
   <si>
     <t>최종 QA · 배포/시연 환경 점검</t>
@@ -667,13 +667,10 @@
     <t>2026-10-16</t>
   </si>
   <si>
-    <t>할 일 · 제출 산출물 일체</t>
+    <t>완료 · 제출 산출물 일체</t>
   </si>
   <si>
     <t>제안서 최종본 제출  [TNSM-78]</t>
-  </si>
-  <si>
-    <t>할 일</t>
   </si>
   <si>
     <t>소스코드 최종 제출  [TNSM-79]</t>
@@ -11361,7 +11358,7 @@
         <v>217</v>
       </c>
       <c r="I105" s="25" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="J105" s="20"/>
       <c r="K105" s="20"/>
@@ -11432,7 +11429,7 @@
       <c r="B106" s="24"/>
       <c r="C106" s="25"/>
       <c r="D106" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="24" t="s">
@@ -11445,7 +11442,7 @@
         <v>217</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -11516,7 +11513,7 @@
       <c r="B107" s="24"/>
       <c r="C107" s="25"/>
       <c r="D107" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="24" t="s">
@@ -11529,7 +11526,7 @@
         <v>217</v>
       </c>
       <c r="I107" s="25" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -11601,10 +11598,10 @@
         <v>4</v>
       </c>
       <c r="C108" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D108" s="16" t="s">
         <v>223</v>
-      </c>
-      <c r="D108" s="16" t="s">
-        <v>224</v>
       </c>
       <c r="E108" s="16"/>
       <c r="F108" s="17" t="s">
@@ -11688,7 +11685,7 @@
       <c r="B109" s="24"/>
       <c r="C109" s="25"/>
       <c r="D109" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="24" t="s">
@@ -11772,7 +11769,7 @@
       <c r="B110" s="24"/>
       <c r="C110" s="25"/>
       <c r="D110" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="24" t="s">
@@ -11856,7 +11853,7 @@
       <c r="B111" s="24"/>
       <c r="C111" s="25"/>
       <c r="D111" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="24" t="s">
@@ -11940,7 +11937,7 @@
       <c r="B112" s="24"/>
       <c r="C112" s="25"/>
       <c r="D112" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="24" t="s">
@@ -12024,7 +12021,7 @@
       <c r="B113" s="24"/>
       <c r="C113" s="25"/>
       <c r="D113" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="24" t="s">
@@ -12108,7 +12105,7 @@
       <c r="B114" s="24"/>
       <c r="C114" s="25"/>
       <c r="D114" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="24" t="s">
@@ -12193,10 +12190,10 @@
         <v>5</v>
       </c>
       <c r="C115" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>231</v>
-      </c>
-      <c r="D115" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17" t="s">
@@ -12209,7 +12206,7 @@
         <v>148</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -12281,23 +12278,23 @@
         <v>6</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E116" s="16"/>
       <c r="F116" s="17" t="s">
         <v>107</v>
       </c>
       <c r="G116" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="H116" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="I116" s="18" t="s">
         <v>235</v>
-      </c>
-      <c r="H116" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="I116" s="18" t="s">
-        <v>236</v>
       </c>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -12369,23 +12366,23 @@
         <v>7</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E117" s="16"/>
       <c r="F117" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>190</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -12457,23 +12454,23 @@
         <v>8</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E118" s="16"/>
       <c r="F118" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H118" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -12545,23 +12542,23 @@
         <v>9</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E119" s="16"/>
       <c r="F119" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>190</v>
       </c>
       <c r="I119" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -12633,23 +12630,23 @@
         <v>10</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E120" s="16"/>
       <c r="F120" s="17" t="s">
         <v>88</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H120" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -12721,23 +12718,23 @@
         <v>11</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E121" s="16"/>
       <c r="F121" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I121" s="18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -12809,10 +12806,10 @@
         <v>12</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E122" s="16"/>
       <c r="F122" s="17" t="s">
@@ -12825,7 +12822,7 @@
         <v>7</v>
       </c>
       <c r="I122" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -12897,10 +12894,10 @@
         <v>13</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E123" s="16"/>
       <c r="F123" s="17" t="s">
@@ -12913,7 +12910,7 @@
         <v>7</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -12981,7 +12978,7 @@
     </row>
     <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B125" s="32"/>
       <c r="C125" s="32"/>
@@ -13014,7 +13011,7 @@
     </row>
     <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B126" s="32"/>
       <c r="C126" s="32"/>
@@ -13047,7 +13044,7 @@
     </row>
     <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B127" s="32"/>
       <c r="C127" s="32"/>
@@ -13080,7 +13077,7 @@
     </row>
     <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B128" s="32"/>
       <c r="C128" s="32"/>
@@ -13113,7 +13110,7 @@
     </row>
     <row r="130" ht="16" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A130" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -13189,1228 +13186,1228 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B131" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="B131" s="33" t="s">
+      <c r="C131" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="C131" s="33" t="s">
+      <c r="D131" s="33" t="s">
         <v>258</v>
-      </c>
-      <c r="D131" s="33" t="s">
-        <v>259</v>
       </c>
       <c r="E131" s="33"/>
       <c r="F131" s="33" t="s">
         <v>25</v>
       </c>
       <c r="G131" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="H131" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="H131" s="33" t="s">
+      <c r="I131" s="33" t="s">
         <v>261</v>
-      </c>
-      <c r="I131" s="33" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="132" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="B132" s="34" t="s">
+      <c r="C132" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="C132" s="25" t="s">
+      <c r="D132" s="25" t="s">
         <v>265</v>
-      </c>
-      <c r="D132" s="25" t="s">
-        <v>266</v>
       </c>
       <c r="E132" s="25"/>
       <c r="F132" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G132" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="H132" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="H132" s="36" t="s">
+      <c r="I132" s="25" t="s">
         <v>268</v>
-      </c>
-      <c r="I132" s="25" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="133" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D133" s="25" t="s">
         <v>270</v>
-      </c>
-      <c r="B133" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="C133" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>271</v>
       </c>
       <c r="E133" s="25"/>
       <c r="F133" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G133" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="H133" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I133" s="25" t="s">
         <v>272</v>
-      </c>
-      <c r="H133" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I133" s="25" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="134" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B134" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E134" s="25"/>
       <c r="F134" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G134" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="H134" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I134" s="25" t="s">
         <v>275</v>
-      </c>
-      <c r="H134" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I134" s="25" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="135" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B135" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C135" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E135" s="25"/>
       <c r="F135" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G135" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="H135" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I135" s="25" t="s">
         <v>278</v>
-      </c>
-      <c r="H135" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I135" s="25" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="136" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B136" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C136" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E136" s="25"/>
       <c r="F136" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G136" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="H136" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I136" s="25" t="s">
         <v>281</v>
-      </c>
-      <c r="H136" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I136" s="25" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="137" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B137" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C137" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D137" s="25" t="s">
         <v>283</v>
-      </c>
-      <c r="D137" s="25" t="s">
-        <v>284</v>
       </c>
       <c r="E137" s="25"/>
       <c r="F137" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G137" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I137" s="25" t="s">
         <v>285</v>
-      </c>
-      <c r="H137" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I137" s="25" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="138" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B138" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E138" s="25"/>
       <c r="F138" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G138" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="H138" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I138" s="25" t="s">
         <v>288</v>
-      </c>
-      <c r="H138" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I138" s="25" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="139" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B139" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C139" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="D139" s="25" t="s">
         <v>290</v>
-      </c>
-      <c r="D139" s="25" t="s">
-        <v>291</v>
       </c>
       <c r="E139" s="25"/>
       <c r="F139" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G139" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="H139" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I139" s="25" t="s">
         <v>292</v>
-      </c>
-      <c r="H139" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I139" s="25" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="140" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B140" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C140" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="D140" s="25" t="s">
         <v>294</v>
-      </c>
-      <c r="D140" s="25" t="s">
-        <v>295</v>
       </c>
       <c r="E140" s="25"/>
       <c r="F140" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G140" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="H140" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I140" s="25" t="s">
         <v>296</v>
-      </c>
-      <c r="H140" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I140" s="25" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="141" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B141" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C141" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="D141" s="25" t="s">
         <v>298</v>
-      </c>
-      <c r="D141" s="25" t="s">
-        <v>299</v>
       </c>
       <c r="E141" s="25"/>
       <c r="F141" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G141" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="H141" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I141" s="25" t="s">
         <v>300</v>
-      </c>
-      <c r="H141" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I141" s="25" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="142" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B142" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C142" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D142" s="25" t="s">
         <v>302</v>
-      </c>
-      <c r="D142" s="25" t="s">
-        <v>303</v>
       </c>
       <c r="E142" s="25"/>
       <c r="F142" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G142" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="H142" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I142" s="25" t="s">
         <v>304</v>
-      </c>
-      <c r="H142" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I142" s="25" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="143" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B143" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E143" s="25"/>
       <c r="F143" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G143" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="H143" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I143" s="25" t="s">
         <v>307</v>
-      </c>
-      <c r="H143" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I143" s="25" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="144" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B144" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="C144" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="C144" s="25" t="s">
+      <c r="D144" s="25" t="s">
         <v>310</v>
-      </c>
-      <c r="D144" s="25" t="s">
-        <v>311</v>
       </c>
       <c r="E144" s="25"/>
       <c r="F144" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G144" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="H144" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I144" s="25" t="s">
         <v>312</v>
-      </c>
-      <c r="H144" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I144" s="25" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="145" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B145" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C145" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="D145" s="25" t="s">
         <v>314</v>
-      </c>
-      <c r="D145" s="25" t="s">
-        <v>315</v>
       </c>
       <c r="E145" s="25"/>
       <c r="F145" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G145" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H145" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I145" s="25" t="s">
         <v>316</v>
-      </c>
-      <c r="H145" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I145" s="25" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="146" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B146" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C146" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="D146" s="25" t="s">
         <v>318</v>
-      </c>
-      <c r="D146" s="25" t="s">
-        <v>319</v>
       </c>
       <c r="E146" s="25"/>
       <c r="F146" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G146" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="H146" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I146" s="25" t="s">
         <v>320</v>
-      </c>
-      <c r="H146" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I146" s="25" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="147" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B147" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E147" s="25"/>
       <c r="F147" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G147" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="H147" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I147" s="25" t="s">
         <v>323</v>
-      </c>
-      <c r="H147" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I147" s="25" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="148" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B148" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E148" s="25"/>
       <c r="F148" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G148" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="H148" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I148" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="H148" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I148" s="25" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="149" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C149" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="D149" s="25" t="s">
         <v>328</v>
-      </c>
-      <c r="D149" s="25" t="s">
-        <v>329</v>
       </c>
       <c r="E149" s="25"/>
       <c r="F149" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G149" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="H149" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I149" s="25" t="s">
         <v>330</v>
-      </c>
-      <c r="H149" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I149" s="25" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="150" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B150" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E150" s="25"/>
       <c r="F150" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G150" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I150" s="25" t="s">
         <v>333</v>
-      </c>
-      <c r="H150" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I150" s="25" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="151" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B151" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E151" s="25"/>
       <c r="F151" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G151" s="35" t="s">
+        <v>335</v>
+      </c>
+      <c r="H151" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I151" s="25" t="s">
         <v>336</v>
-      </c>
-      <c r="H151" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I151" s="25" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="152" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B152" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E152" s="25"/>
       <c r="F152" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G152" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="H152" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I152" s="25" t="s">
         <v>339</v>
-      </c>
-      <c r="H152" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I152" s="25" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="153" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B153" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E153" s="25"/>
       <c r="F153" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G153" s="35" t="s">
+        <v>341</v>
+      </c>
+      <c r="H153" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I153" s="25" t="s">
         <v>342</v>
-      </c>
-      <c r="H153" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I153" s="25" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="154" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B154" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C154" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="D154" s="25" t="s">
         <v>344</v>
-      </c>
-      <c r="D154" s="25" t="s">
-        <v>345</v>
       </c>
       <c r="E154" s="25"/>
       <c r="F154" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G154" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="H154" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I154" s="25" t="s">
         <v>346</v>
-      </c>
-      <c r="H154" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I154" s="25" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="155" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B155" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E155" s="25"/>
       <c r="F155" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G155" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="H155" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I155" s="25" t="s">
         <v>349</v>
-      </c>
-      <c r="H155" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I155" s="25" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="156" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B156" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E156" s="25"/>
       <c r="F156" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G156" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="H156" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I156" s="25" t="s">
         <v>352</v>
-      </c>
-      <c r="H156" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I156" s="25" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="157" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B157" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="C157" s="25" t="s">
         <v>354</v>
       </c>
-      <c r="C157" s="25" t="s">
+      <c r="D157" s="25" t="s">
         <v>355</v>
-      </c>
-      <c r="D157" s="25" t="s">
-        <v>356</v>
       </c>
       <c r="E157" s="25"/>
       <c r="F157" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G157" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="H157" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I157" s="25" t="s">
         <v>357</v>
-      </c>
-      <c r="H157" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I157" s="25" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="158" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B158" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E158" s="25"/>
       <c r="F158" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G158" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="H158" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I158" s="25" t="s">
         <v>360</v>
-      </c>
-      <c r="H158" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I158" s="25" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="159" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B159" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E159" s="25"/>
       <c r="F159" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G159" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="H159" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I159" s="25" t="s">
         <v>363</v>
-      </c>
-      <c r="H159" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I159" s="25" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="160" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B160" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E160" s="25"/>
       <c r="F160" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G160" s="35" t="s">
+        <v>365</v>
+      </c>
+      <c r="H160" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I160" s="25" t="s">
         <v>366</v>
-      </c>
-      <c r="H160" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I160" s="25" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="161" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B161" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E161" s="25"/>
       <c r="F161" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G161" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="H161" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I161" s="25" t="s">
         <v>369</v>
-      </c>
-      <c r="H161" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I161" s="25" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="162" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B162" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E162" s="25"/>
       <c r="F162" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G162" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="H162" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I162" s="25" t="s">
         <v>372</v>
-      </c>
-      <c r="H162" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I162" s="25" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="163" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B163" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E163" s="25"/>
       <c r="F163" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G163" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="H163" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I163" s="25" t="s">
         <v>375</v>
-      </c>
-      <c r="H163" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I163" s="25" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="164" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B164" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E164" s="25"/>
       <c r="F164" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G164" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="H164" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I164" s="25" t="s">
         <v>378</v>
-      </c>
-      <c r="H164" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I164" s="25" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="165" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D165" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E165" s="25"/>
       <c r="F165" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G165" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="H165" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I165" s="25" t="s">
         <v>381</v>
-      </c>
-      <c r="H165" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I165" s="25" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="166" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B166" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D166" s="25" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E166" s="25"/>
       <c r="F166" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G166" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="H166" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I166" s="25" t="s">
         <v>384</v>
-      </c>
-      <c r="H166" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I166" s="25" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="167" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B167" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C167" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="D167" s="25" t="s">
         <v>386</v>
-      </c>
-      <c r="D167" s="25" t="s">
-        <v>387</v>
       </c>
       <c r="E167" s="25"/>
       <c r="F167" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G167" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="H167" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I167" s="25" t="s">
         <v>388</v>
-      </c>
-      <c r="H167" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I167" s="25" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="168" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B168" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C168" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="D168" s="25" t="s">
         <v>390</v>
-      </c>
-      <c r="D168" s="25" t="s">
-        <v>391</v>
       </c>
       <c r="E168" s="25"/>
       <c r="F168" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G168" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="H168" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I168" s="25" t="s">
         <v>392</v>
-      </c>
-      <c r="H168" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I168" s="25" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="169" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B169" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D169" s="25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E169" s="25"/>
       <c r="F169" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G169" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="H169" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I169" s="25" t="s">
         <v>395</v>
-      </c>
-      <c r="H169" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I169" s="25" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="170" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B170" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E170" s="25"/>
       <c r="F170" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G170" s="35" t="s">
+        <v>397</v>
+      </c>
+      <c r="H170" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I170" s="25" t="s">
         <v>398</v>
-      </c>
-      <c r="H170" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I170" s="25" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="171" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B171" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D171" s="25" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E171" s="25"/>
       <c r="F171" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G171" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="H171" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I171" s="25" t="s">
         <v>401</v>
-      </c>
-      <c r="H171" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I171" s="25" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="172" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B172" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C172" s="25" t="s">
+        <v>402</v>
+      </c>
+      <c r="D172" s="25" t="s">
         <v>403</v>
-      </c>
-      <c r="D172" s="25" t="s">
-        <v>404</v>
       </c>
       <c r="E172" s="25"/>
       <c r="F172" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G172" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="H172" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I172" s="25" t="s">
         <v>405</v>
-      </c>
-      <c r="H172" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I172" s="25" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="173" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B173" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="C173" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="C173" s="25" t="s">
+      <c r="D173" s="25" t="s">
         <v>408</v>
-      </c>
-      <c r="D173" s="25" t="s">
-        <v>409</v>
       </c>
       <c r="E173" s="25"/>
       <c r="F173" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G173" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="H173" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I173" s="25" t="s">
         <v>410</v>
-      </c>
-      <c r="H173" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I173" s="25" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="174" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B174" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E174" s="25"/>
       <c r="F174" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G174" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="H174" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I174" s="25" t="s">
         <v>413</v>
-      </c>
-      <c r="H174" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I174" s="25" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="175" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B175" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D175" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E175" s="25"/>
       <c r="F175" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G175" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="H175" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I175" s="25" t="s">
         <v>416</v>
-      </c>
-      <c r="H175" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I175" s="25" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="176" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B176" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D176" s="25" t="s">
         <v>156</v>
@@ -14420,1206 +14417,1206 @@
         <v>107</v>
       </c>
       <c r="G176" s="35" t="s">
+        <v>417</v>
+      </c>
+      <c r="H176" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I176" s="25" t="s">
         <v>418</v>
-      </c>
-      <c r="H176" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I176" s="25" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="177" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B177" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C177" s="25" t="s">
+        <v>419</v>
+      </c>
+      <c r="D177" s="25" t="s">
         <v>420</v>
-      </c>
-      <c r="D177" s="25" t="s">
-        <v>421</v>
       </c>
       <c r="E177" s="25"/>
       <c r="F177" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G177" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="H177" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I177" s="25" t="s">
         <v>422</v>
-      </c>
-      <c r="H177" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I177" s="25" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="178" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B178" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D178" s="25" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E178" s="25"/>
       <c r="F178" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G178" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="H178" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I178" s="25" t="s">
         <v>425</v>
-      </c>
-      <c r="H178" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I178" s="25" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="179" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B179" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C179" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E179" s="25"/>
       <c r="F179" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G179" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="H179" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I179" s="25" t="s">
         <v>428</v>
-      </c>
-      <c r="H179" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I179" s="25" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="180" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B180" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C180" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="D180" s="25" t="s">
         <v>430</v>
-      </c>
-      <c r="D180" s="25" t="s">
-        <v>431</v>
       </c>
       <c r="E180" s="25"/>
       <c r="F180" s="35" t="s">
         <v>107</v>
       </c>
       <c r="G180" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="H180" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I180" s="25" t="s">
         <v>432</v>
-      </c>
-      <c r="H180" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I180" s="25" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="181" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B181" s="34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C181" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="D181" s="25" t="s">
         <v>434</v>
-      </c>
-      <c r="D181" s="25" t="s">
-        <v>435</v>
       </c>
       <c r="E181" s="25"/>
       <c r="F181" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G181" s="35" t="s">
+        <v>435</v>
+      </c>
+      <c r="H181" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I181" s="25" t="s">
         <v>436</v>
-      </c>
-      <c r="H181" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I181" s="25" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="182" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D182" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E182" s="25"/>
       <c r="F182" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G182" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="H182" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I182" s="25" t="s">
         <v>439</v>
-      </c>
-      <c r="H182" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I182" s="25" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="183" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E183" s="25"/>
       <c r="F183" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G183" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="H183" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I183" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="H183" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I183" s="25" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="184" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B184" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C184" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D184" s="25" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E184" s="25"/>
       <c r="F184" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G184" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="H184" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="H184" s="37" t="s">
+      <c r="I184" s="25" t="s">
         <v>446</v>
-      </c>
-      <c r="I184" s="25" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="185" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B185" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="C185" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="C185" s="25" t="s">
+      <c r="D185" s="25" t="s">
         <v>449</v>
-      </c>
-      <c r="D185" s="25" t="s">
-        <v>450</v>
       </c>
       <c r="E185" s="25"/>
       <c r="F185" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="G185" s="35" t="s">
         <v>451</v>
       </c>
-      <c r="G185" s="35" t="s">
+      <c r="H185" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I185" s="25" t="s">
         <v>452</v>
-      </c>
-      <c r="H185" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I185" s="25" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="186" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C186" s="25" t="s">
+        <v>453</v>
+      </c>
+      <c r="D186" s="25" t="s">
         <v>454</v>
-      </c>
-      <c r="D186" s="25" t="s">
-        <v>455</v>
       </c>
       <c r="E186" s="25"/>
       <c r="F186" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G186" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="H186" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I186" s="25" t="s">
         <v>456</v>
-      </c>
-      <c r="H186" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I186" s="25" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="187" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B187" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C187" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="D187" s="25" t="s">
         <v>458</v>
-      </c>
-      <c r="D187" s="25" t="s">
-        <v>459</v>
       </c>
       <c r="E187" s="25"/>
       <c r="F187" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G187" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="H187" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I187" s="25" t="s">
         <v>460</v>
-      </c>
-      <c r="H187" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I187" s="25" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="188" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B188" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E188" s="25"/>
       <c r="F188" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G188" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="H188" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I188" s="25" t="s">
         <v>463</v>
-      </c>
-      <c r="H188" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I188" s="25" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="189" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B189" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C189" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="D189" s="25" t="s">
         <v>465</v>
-      </c>
-      <c r="D189" s="25" t="s">
-        <v>466</v>
       </c>
       <c r="E189" s="25"/>
       <c r="F189" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G189" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="H189" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I189" s="25" t="s">
         <v>467</v>
-      </c>
-      <c r="H189" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I189" s="25" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="190" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B190" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C190" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="D190" s="25" t="s">
         <v>469</v>
-      </c>
-      <c r="D190" s="25" t="s">
-        <v>470</v>
       </c>
       <c r="E190" s="25"/>
       <c r="F190" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G190" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="H190" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I190" s="25" t="s">
         <v>471</v>
-      </c>
-      <c r="H190" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I190" s="25" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="191" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B191" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E191" s="25"/>
       <c r="F191" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G191" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="H191" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I191" s="25" t="s">
         <v>474</v>
-      </c>
-      <c r="H191" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I191" s="25" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="192" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B192" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C192" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="D192" s="25" t="s">
         <v>476</v>
-      </c>
-      <c r="D192" s="25" t="s">
-        <v>477</v>
       </c>
       <c r="E192" s="25"/>
       <c r="F192" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G192" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="H192" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I192" s="25" t="s">
         <v>478</v>
-      </c>
-      <c r="H192" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I192" s="25" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="193" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B193" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C193" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="D193" s="25" t="s">
         <v>480</v>
-      </c>
-      <c r="D193" s="25" t="s">
-        <v>481</v>
       </c>
       <c r="E193" s="25"/>
       <c r="F193" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G193" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="H193" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I193" s="25" t="s">
         <v>482</v>
-      </c>
-      <c r="H193" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I193" s="25" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="194" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B194" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C194" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="D194" s="25" t="s">
         <v>484</v>
-      </c>
-      <c r="D194" s="25" t="s">
-        <v>485</v>
       </c>
       <c r="E194" s="25"/>
       <c r="F194" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G194" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="H194" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I194" s="25" t="s">
         <v>486</v>
-      </c>
-      <c r="H194" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I194" s="25" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="195" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B195" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C195" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="D195" s="25" t="s">
         <v>488</v>
-      </c>
-      <c r="D195" s="25" t="s">
-        <v>489</v>
       </c>
       <c r="E195" s="25"/>
       <c r="F195" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G195" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="H195" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I195" s="25" t="s">
         <v>490</v>
-      </c>
-      <c r="H195" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I195" s="25" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="196" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B196" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="C196" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="C196" s="25" t="s">
+      <c r="D196" s="25" t="s">
         <v>493</v>
-      </c>
-      <c r="D196" s="25" t="s">
-        <v>494</v>
       </c>
       <c r="E196" s="25"/>
       <c r="F196" s="35" t="s">
+        <v>494</v>
+      </c>
+      <c r="G196" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="G196" s="35" t="s">
+      <c r="H196" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I196" s="25" t="s">
         <v>496</v>
-      </c>
-      <c r="H196" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I196" s="25" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="197" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B197" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D197" s="25" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E197" s="25"/>
       <c r="F197" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G197" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="H197" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I197" s="25" t="s">
         <v>499</v>
-      </c>
-      <c r="H197" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I197" s="25" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="198" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B198" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E198" s="25"/>
       <c r="F198" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G198" s="35" t="s">
+        <v>501</v>
+      </c>
+      <c r="H198" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I198" s="25" t="s">
         <v>502</v>
-      </c>
-      <c r="H198" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I198" s="25" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="199" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B199" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E199" s="25"/>
       <c r="F199" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G199" s="35" t="s">
+        <v>504</v>
+      </c>
+      <c r="H199" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I199" s="25" t="s">
         <v>505</v>
-      </c>
-      <c r="H199" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I199" s="25" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="200" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B200" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C200" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="D200" s="25" t="s">
         <v>507</v>
-      </c>
-      <c r="D200" s="25" t="s">
-        <v>508</v>
       </c>
       <c r="E200" s="25"/>
       <c r="F200" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G200" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="H200" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I200" s="25" t="s">
         <v>509</v>
-      </c>
-      <c r="H200" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I200" s="25" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="201" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B201" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C201" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="D201" s="25" t="s">
         <v>511</v>
-      </c>
-      <c r="D201" s="25" t="s">
-        <v>512</v>
       </c>
       <c r="E201" s="25"/>
       <c r="F201" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G201" s="35" t="s">
+        <v>512</v>
+      </c>
+      <c r="H201" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I201" s="25" t="s">
         <v>513</v>
-      </c>
-      <c r="H201" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I201" s="25" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="202" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B202" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D202" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E202" s="25"/>
       <c r="F202" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G202" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="H202" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I202" s="25" t="s">
         <v>516</v>
-      </c>
-      <c r="H202" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I202" s="25" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="203" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B203" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E203" s="25"/>
       <c r="F203" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G203" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="H203" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I203" s="25" t="s">
         <v>519</v>
-      </c>
-      <c r="H203" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I203" s="25" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="204" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B204" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C204" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="D204" s="25" t="s">
         <v>521</v>
-      </c>
-      <c r="D204" s="25" t="s">
-        <v>522</v>
       </c>
       <c r="E204" s="25"/>
       <c r="F204" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G204" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="H204" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I204" s="25" t="s">
         <v>523</v>
-      </c>
-      <c r="H204" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I204" s="25" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="205" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B205" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C205" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="D205" s="25" t="s">
         <v>525</v>
-      </c>
-      <c r="D205" s="25" t="s">
-        <v>526</v>
       </c>
       <c r="E205" s="25"/>
       <c r="F205" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G205" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="H205" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I205" s="25" t="s">
         <v>527</v>
-      </c>
-      <c r="H205" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I205" s="25" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="206" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B206" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C206" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="D206" s="25" t="s">
         <v>529</v>
-      </c>
-      <c r="D206" s="25" t="s">
-        <v>530</v>
       </c>
       <c r="E206" s="25"/>
       <c r="F206" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G206" s="35" t="s">
+        <v>530</v>
+      </c>
+      <c r="H206" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I206" s="25" t="s">
         <v>531</v>
-      </c>
-      <c r="H206" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I206" s="25" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="207" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B207" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C207" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="D207" s="25" t="s">
         <v>533</v>
-      </c>
-      <c r="D207" s="25" t="s">
-        <v>534</v>
       </c>
       <c r="E207" s="25"/>
       <c r="F207" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G207" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="H207" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I207" s="25" t="s">
         <v>535</v>
-      </c>
-      <c r="H207" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I207" s="25" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="208" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B208" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="C208" s="25" t="s">
         <v>537</v>
       </c>
-      <c r="C208" s="25" t="s">
+      <c r="D208" s="25" t="s">
         <v>538</v>
-      </c>
-      <c r="D208" s="25" t="s">
-        <v>539</v>
       </c>
       <c r="E208" s="25"/>
       <c r="F208" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G208" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="H208" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I208" s="25" t="s">
         <v>540</v>
-      </c>
-      <c r="H208" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I208" s="25" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="209" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B209" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D209" s="25" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E209" s="25"/>
       <c r="F209" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G209" s="35" t="s">
+        <v>542</v>
+      </c>
+      <c r="H209" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I209" s="25" t="s">
         <v>543</v>
-      </c>
-      <c r="H209" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I209" s="25" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="210" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B210" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C210" s="25" t="s">
         <v>66</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E210" s="25"/>
       <c r="F210" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G210" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="H210" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="I210" s="25" t="s">
         <v>546</v>
-      </c>
-      <c r="H210" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="I210" s="25" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="211" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B211" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="C211" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="C211" s="25" t="s">
+      <c r="D211" s="25" t="s">
         <v>549</v>
-      </c>
-      <c r="D211" s="25" t="s">
-        <v>550</v>
       </c>
       <c r="E211" s="25"/>
       <c r="F211" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G211" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="H211" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I211" s="25" t="s">
         <v>551</v>
-      </c>
-      <c r="H211" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I211" s="25" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="212" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B212" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C212" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="D212" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="D212" s="25" t="s">
-        <v>554</v>
       </c>
       <c r="E212" s="25"/>
       <c r="F212" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G212" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="H212" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I212" s="25" t="s">
         <v>555</v>
-      </c>
-      <c r="H212" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I212" s="25" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="213" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B213" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C213" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="D213" s="25" t="s">
         <v>557</v>
-      </c>
-      <c r="D213" s="25" t="s">
-        <v>558</v>
       </c>
       <c r="E213" s="25"/>
       <c r="F213" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G213" s="35" t="s">
+        <v>558</v>
+      </c>
+      <c r="H213" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I213" s="25" t="s">
         <v>559</v>
-      </c>
-      <c r="H213" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I213" s="25" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="214" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="34" t="s">
+        <v>560</v>
+      </c>
+      <c r="B214" s="34" t="s">
         <v>561</v>
       </c>
-      <c r="B214" s="34" t="s">
+      <c r="C214" s="25" t="s">
         <v>562</v>
       </c>
-      <c r="C214" s="25" t="s">
+      <c r="D214" s="25" t="s">
         <v>563</v>
-      </c>
-      <c r="D214" s="25" t="s">
-        <v>564</v>
       </c>
       <c r="E214" s="25"/>
       <c r="F214" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G214" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="H214" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I214" s="25" t="s">
         <v>565</v>
-      </c>
-      <c r="H214" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I214" s="25" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="215" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B215" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C215" s="25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D215" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E215" s="25"/>
       <c r="F215" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G215" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="H215" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I215" s="25" t="s">
         <v>568</v>
-      </c>
-      <c r="H215" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I215" s="25" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="216" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B216" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C216" s="25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D216" s="25" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E216" s="25"/>
       <c r="F216" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G216" s="35" t="s">
+        <v>570</v>
+      </c>
+      <c r="H216" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I216" s="25" t="s">
         <v>571</v>
-      </c>
-      <c r="H216" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I216" s="25" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="217" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B217" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C217" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="D217" s="25" t="s">
         <v>573</v>
-      </c>
-      <c r="D217" s="25" t="s">
-        <v>574</v>
       </c>
       <c r="E217" s="25"/>
       <c r="F217" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G217" s="35" t="s">
+        <v>574</v>
+      </c>
+      <c r="H217" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I217" s="25" t="s">
         <v>575</v>
-      </c>
-      <c r="H217" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I217" s="25" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="218" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B218" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C218" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="D218" s="25" t="s">
         <v>577</v>
-      </c>
-      <c r="D218" s="25" t="s">
-        <v>578</v>
       </c>
       <c r="E218" s="25"/>
       <c r="F218" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G218" s="35" t="s">
+        <v>578</v>
+      </c>
+      <c r="H218" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I218" s="25" t="s">
         <v>579</v>
-      </c>
-      <c r="H218" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I218" s="25" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="219" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B219" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C219" s="25" t="s">
+        <v>580</v>
+      </c>
+      <c r="D219" s="25" t="s">
         <v>581</v>
-      </c>
-      <c r="D219" s="25" t="s">
-        <v>582</v>
       </c>
       <c r="E219" s="25"/>
       <c r="F219" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G219" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="H219" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I219" s="25" t="s">
         <v>583</v>
-      </c>
-      <c r="H219" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I219" s="25" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="220" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B220" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C220" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E220" s="25"/>
       <c r="F220" s="35" t="s">
         <v>40</v>
       </c>
       <c r="G220" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="H220" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I220" s="25" t="s">
         <v>586</v>
-      </c>
-      <c r="H220" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="I220" s="25" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="38" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B221" s="38"/>
       <c r="C221" s="38"/>
